--- a/attendance_report.xlsx
+++ b/attendance_report.xlsx
@@ -483,7 +483,7 @@
     <row r="1" ht="17" customHeight="0">
       <c s="1" t="inlineStr" r="B1">
         <is>
-          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 28-10-2026</t>
+          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 31-10-2026</t>
         </is>
       </c>
       <c s="2" t="inlineStr" r="P1">
@@ -493,7 +493,7 @@
       </c>
       <c s="3" t="inlineStr" r="AF1">
         <is>
-          <t xml:space="preserve">Print Date 28-10-2026</t>
+          <t xml:space="preserve">Print Date 31-10-2026</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       <c s="13" t="str" r="N7"/>
       <c s="12" t="inlineStr" r="O7">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c s="13" t="str" r="P7"/>
@@ -711,7 +711,7 @@
       <c s="13" t="str" r="U7"/>
       <c s="12" t="inlineStr" r="V7">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c s="13" t="str" r="W7"/>
@@ -729,7 +729,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB7">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c s="13" t="str" r="AC7"/>
@@ -740,7 +740,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE7">
         <is>
-          <t xml:space="preserve">39:22</t>
+          <t xml:space="preserve">42:18</t>
         </is>
       </c>
       <c s="13" t="str" r="AF7"/>
@@ -910,9 +910,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ8"/>
-      <c s="15" t="str" r="AK8"/>
-      <c s="15" t="str" r="AL8"/>
+      <c s="15" t="inlineStr" r="AJ8">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK8">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL8">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM8"/>
     </row>
     <row r="9" ht="15.3" customHeight="0">
@@ -1065,9 +1077,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ9"/>
-      <c s="18" t="str" r="AK9"/>
-      <c s="20" t="str" r="AL9"/>
+      <c s="18" t="inlineStr" r="AJ9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL9">
+        <is>
+          <t xml:space="preserve">13:56</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM9"/>
     </row>
     <row r="10" ht="15.3" customHeight="0">
@@ -1220,9 +1244,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ10"/>
-      <c s="20" t="str" r="AK10"/>
-      <c s="20" t="str" r="AL10"/>
+      <c s="20" t="inlineStr" r="AJ10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM10"/>
     </row>
     <row r="11" ht="15.35" customHeight="0">
@@ -1375,9 +1411,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ11"/>
-      <c s="20" t="str" r="AK11"/>
-      <c s="20" t="str" r="AL11"/>
+      <c s="20" t="inlineStr" r="AJ11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM11"/>
     </row>
     <row r="12" ht="15.3" customHeight="0">
@@ -1530,9 +1578,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ12"/>
-      <c s="20" t="str" r="AK12"/>
-      <c s="20" t="str" r="AL12"/>
+      <c s="20" t="inlineStr" r="AJ12">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK12">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL12">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM12"/>
     </row>
     <row r="13" ht="14.6" customHeight="0">
@@ -1685,9 +1745,21 @@
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ13"/>
-      <c s="20" t="str" r="AK13"/>
-      <c s="20" t="str" r="AL13"/>
+      <c s="20" t="inlineStr" r="AJ13">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK13">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL13">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM13"/>
     </row>
     <row r="14" ht="14.6" customHeight="0">
@@ -1840,9 +1912,21 @@
           <t xml:space="preserve">001</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ14"/>
-      <c s="24" t="str" r="AK14"/>
-      <c s="24" t="str" r="AL14"/>
+      <c s="24" t="inlineStr" r="AJ14">
+        <is>
+          <t xml:space="preserve">001</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK14">
+        <is>
+          <t xml:space="preserve">001</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL14">
+        <is>
+          <t xml:space="preserve">001</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM14"/>
     </row>
     <row r="15" ht="15.3" customHeight="0">
@@ -1974,7 +2058,7 @@
       <c s="13" t="str" r="N17"/>
       <c s="12" t="inlineStr" r="O17">
         <is>
-          <t xml:space="preserve">20.5</t>
+          <t xml:space="preserve">21.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P17"/>
@@ -1993,7 +2077,7 @@
       <c s="13" t="str" r="U17"/>
       <c s="12" t="inlineStr" r="V17">
         <is>
-          <t xml:space="preserve">2.5</t>
+          <t xml:space="preserve">4.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W17"/>
@@ -2011,7 +2095,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB17">
         <is>
-          <t xml:space="preserve">25.5</t>
+          <t xml:space="preserve">26.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC17"/>
@@ -2022,7 +2106,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE17">
         <is>
-          <t xml:space="preserve">17:26</t>
+          <t xml:space="preserve">17:53</t>
         </is>
       </c>
       <c s="13" t="str" r="AF17"/>
@@ -2196,9 +2280,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ18"/>
-      <c s="15" t="str" r="AK18"/>
-      <c s="15" t="str" r="AL18"/>
+      <c s="15" t="inlineStr" r="AJ18">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK18">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL18">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM18"/>
     </row>
     <row r="19" ht="15.35" customHeight="0">
@@ -2351,9 +2447,21 @@
           <t xml:space="preserve">11:54</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ19"/>
-      <c s="18" t="str" r="AK19"/>
-      <c s="20" t="str" r="AL19"/>
+      <c s="18" t="inlineStr" r="AJ19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL19">
+        <is>
+          <t xml:space="preserve">11:57</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM19"/>
     </row>
     <row r="20" ht="15.3" customHeight="0">
@@ -2506,9 +2614,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ20"/>
-      <c s="20" t="str" r="AK20"/>
-      <c s="20" t="str" r="AL20"/>
+      <c s="20" t="inlineStr" r="AJ20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM20"/>
     </row>
     <row r="21" ht="15.35" customHeight="0">
@@ -2661,9 +2781,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ21"/>
-      <c s="20" t="str" r="AK21"/>
-      <c s="20" t="str" r="AL21"/>
+      <c s="20" t="inlineStr" r="AJ21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM21"/>
     </row>
     <row r="22" ht="15.3" customHeight="0">
@@ -2816,9 +2948,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ22"/>
-      <c s="20" t="str" r="AK22"/>
-      <c s="20" t="str" r="AL22"/>
+      <c s="20" t="inlineStr" r="AJ22">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK22">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL22">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM22"/>
     </row>
     <row r="23" ht="14.6" customHeight="0">
@@ -2971,9 +3115,21 @@
           <t xml:space="preserve">P-LT</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ23"/>
-      <c s="20" t="str" r="AK23"/>
-      <c s="20" t="str" r="AL23"/>
+      <c s="20" t="inlineStr" r="AJ23">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK23">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL23">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM23"/>
     </row>
     <row r="24" ht="14.6" customHeight="0">
@@ -3126,9 +3282,21 @@
           <t xml:space="preserve">003</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ24"/>
-      <c s="24" t="str" r="AK24"/>
-      <c s="24" t="str" r="AL24"/>
+      <c s="24" t="inlineStr" r="AJ24">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK24">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL24">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM24"/>
     </row>
     <row r="25" ht="15.3" customHeight="0">
@@ -3260,7 +3428,7 @@
       <c s="13" t="str" r="N27"/>
       <c s="12" t="inlineStr" r="O27">
         <is>
-          <t xml:space="preserve">17.5</t>
+          <t xml:space="preserve">18.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P27"/>
@@ -3279,7 +3447,7 @@
       <c s="13" t="str" r="U27"/>
       <c s="12" t="inlineStr" r="V27">
         <is>
-          <t xml:space="preserve">5.5</t>
+          <t xml:space="preserve">7.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W27"/>
@@ -3297,7 +3465,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB27">
         <is>
-          <t xml:space="preserve">22.5</t>
+          <t xml:space="preserve">23.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC27"/>
@@ -3320,13 +3488,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI27">
         <is>
-          <t xml:space="preserve">123:54</t>
+          <t xml:space="preserve">133:4</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ27"/>
       <c s="12" t="inlineStr" r="AK27">
         <is>
-          <t xml:space="preserve">8:8</t>
+          <t xml:space="preserve">8:18</t>
         </is>
       </c>
       <c s="13" t="str" r="AL27"/>
@@ -3482,9 +3650,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ28"/>
-      <c s="15" t="str" r="AK28"/>
-      <c s="15" t="str" r="AL28"/>
+      <c s="15" t="inlineStr" r="AJ28">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK28">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL28">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM28"/>
     </row>
     <row r="29" ht="15.35" customHeight="0">
@@ -3613,7 +3793,7 @@
       </c>
       <c s="18" t="inlineStr" r="AD29">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:50</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AE29">
@@ -3637,9 +3817,21 @@
           <t xml:space="preserve">12:08</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ29"/>
-      <c s="18" t="str" r="AK29"/>
-      <c s="20" t="str" r="AL29"/>
+      <c s="18" t="inlineStr" r="AJ29">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK29">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL29">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM29"/>
     </row>
     <row r="30" ht="15.3" customHeight="0">
@@ -3768,7 +3960,7 @@
       </c>
       <c s="20" t="inlineStr" r="AD30">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AE30">
@@ -3792,9 +3984,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ30"/>
-      <c s="20" t="str" r="AK30"/>
-      <c s="20" t="str" r="AL30"/>
+      <c s="20" t="inlineStr" r="AJ30">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK30">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL30">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM30"/>
     </row>
     <row r="31" ht="15.35" customHeight="0">
@@ -3923,7 +4127,7 @@
       </c>
       <c s="20" t="inlineStr" r="AD31">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:10</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AE31">
@@ -3947,9 +4151,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ31"/>
-      <c s="20" t="str" r="AK31"/>
-      <c s="20" t="str" r="AL31"/>
+      <c s="20" t="inlineStr" r="AJ31">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK31">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL31">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM31"/>
     </row>
     <row r="32" ht="15.3" customHeight="0">
@@ -4078,7 +4294,7 @@
       </c>
       <c s="20" t="inlineStr" r="AD32">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:10</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AE32">
@@ -4102,9 +4318,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ32"/>
-      <c s="20" t="str" r="AK32"/>
-      <c s="20" t="str" r="AL32"/>
+      <c s="20" t="inlineStr" r="AJ32">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK32">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL32">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM32"/>
     </row>
     <row r="33" ht="14.6" customHeight="0">
@@ -4233,7 +4461,7 @@
       </c>
       <c s="20" t="inlineStr" r="AD33">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AE33">
@@ -4257,9 +4485,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ33"/>
-      <c s="20" t="str" r="AK33"/>
-      <c s="20" t="str" r="AL33"/>
+      <c s="20" t="inlineStr" r="AJ33">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK33">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL33">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM33"/>
     </row>
     <row r="34" ht="14.6" customHeight="0">
@@ -4412,9 +4652,21 @@
           <t xml:space="preserve">005</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ34"/>
-      <c s="24" t="str" r="AK34"/>
-      <c s="24" t="str" r="AL34"/>
+      <c s="24" t="inlineStr" r="AJ34">
+        <is>
+          <t xml:space="preserve">005</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK34">
+        <is>
+          <t xml:space="preserve">005</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL34">
+        <is>
+          <t xml:space="preserve">005</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM34"/>
     </row>
     <row r="35" ht="15.3" customHeight="0">
@@ -4546,7 +4798,7 @@
       <c s="13" t="str" r="N37"/>
       <c s="12" t="inlineStr" r="O37">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c s="13" t="str" r="P37"/>
@@ -4565,7 +4817,7 @@
       <c s="13" t="str" r="U37"/>
       <c s="12" t="inlineStr" r="V37">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c s="13" t="str" r="W37"/>
@@ -4583,7 +4835,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB37">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c s="13" t="str" r="AC37"/>
@@ -4768,9 +5020,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ38"/>
-      <c s="15" t="str" r="AK38"/>
-      <c s="15" t="str" r="AL38"/>
+      <c s="15" t="inlineStr" r="AJ38">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK38">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL38">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM38"/>
     </row>
     <row r="39" ht="15.35" customHeight="0">
@@ -4923,9 +5187,21 @@
           <t xml:space="preserve">11:53</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ39"/>
-      <c s="18" t="str" r="AK39"/>
-      <c s="20" t="str" r="AL39"/>
+      <c s="18" t="inlineStr" r="AJ39">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK39">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL39">
+        <is>
+          <t xml:space="preserve">11:57</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM39"/>
     </row>
     <row r="40" ht="15.3" customHeight="0">
@@ -5078,9 +5354,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ40"/>
-      <c s="20" t="str" r="AK40"/>
-      <c s="20" t="str" r="AL40"/>
+      <c s="20" t="inlineStr" r="AJ40">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK40">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL40">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM40"/>
     </row>
     <row r="41" ht="15.3" customHeight="0">
@@ -5233,9 +5521,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ41"/>
-      <c s="20" t="str" r="AK41"/>
-      <c s="20" t="str" r="AL41"/>
+      <c s="20" t="inlineStr" r="AJ41">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK41">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL41">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM41"/>
     </row>
     <row r="42" ht="15.35" customHeight="0">
@@ -5388,9 +5688,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ42"/>
-      <c s="20" t="str" r="AK42"/>
-      <c s="20" t="str" r="AL42"/>
+      <c s="20" t="inlineStr" r="AJ42">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK42">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL42">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM42"/>
     </row>
     <row r="43" ht="14.6" customHeight="0">
@@ -5543,9 +5855,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ43"/>
-      <c s="20" t="str" r="AK43"/>
-      <c s="20" t="str" r="AL43"/>
+      <c s="20" t="inlineStr" r="AJ43">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK43">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL43">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM43"/>
     </row>
     <row r="44" ht="14.6" customHeight="0">
@@ -5698,9 +6022,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ44"/>
-      <c s="24" t="str" r="AK44"/>
-      <c s="24" t="str" r="AL44"/>
+      <c s="24" t="inlineStr" r="AJ44">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK44">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL44">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM44"/>
     </row>
     <row r="45" ht="15.3" customHeight="0">
@@ -5832,7 +6168,7 @@
       <c s="13" t="str" r="N47"/>
       <c s="12" t="inlineStr" r="O47">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c s="13" t="str" r="P47"/>
@@ -5851,7 +6187,7 @@
       <c s="13" t="str" r="U47"/>
       <c s="12" t="inlineStr" r="V47">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c s="13" t="str" r="W47"/>
@@ -5869,7 +6205,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB47">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c s="13" t="str" r="AC47"/>
@@ -6054,9 +6390,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ48"/>
-      <c s="15" t="str" r="AK48"/>
-      <c s="15" t="str" r="AL48"/>
+      <c s="15" t="inlineStr" r="AJ48">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK48">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL48">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM48"/>
     </row>
     <row r="49" ht="15.35" customHeight="0">
@@ -6209,9 +6557,21 @@
           <t xml:space="preserve">11:40</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ49"/>
-      <c s="18" t="str" r="AK49"/>
-      <c s="20" t="str" r="AL49"/>
+      <c s="18" t="inlineStr" r="AJ49">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK49">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL49">
+        <is>
+          <t xml:space="preserve">11:08</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM49"/>
     </row>
     <row r="50" ht="15.3" customHeight="0">
@@ -6364,9 +6724,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ50"/>
-      <c s="20" t="str" r="AK50"/>
-      <c s="20" t="str" r="AL50"/>
+      <c s="20" t="inlineStr" r="AJ50">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK50">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL50">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM50"/>
     </row>
     <row r="51" ht="15.3" customHeight="0">
@@ -6519,9 +6891,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ51"/>
-      <c s="20" t="str" r="AK51"/>
-      <c s="20" t="str" r="AL51"/>
+      <c s="20" t="inlineStr" r="AJ51">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK51">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL51">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM51"/>
     </row>
     <row r="52" ht="15.35" customHeight="0">
@@ -6674,9 +7058,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ52"/>
-      <c s="20" t="str" r="AK52"/>
-      <c s="20" t="str" r="AL52"/>
+      <c s="20" t="inlineStr" r="AJ52">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK52">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL52">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM52"/>
     </row>
     <row r="53" ht="14.6" customHeight="0">
@@ -6829,9 +7225,21 @@
           <t xml:space="preserve">P-LT</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ53"/>
-      <c s="20" t="str" r="AK53"/>
-      <c s="20" t="str" r="AL53"/>
+      <c s="20" t="inlineStr" r="AJ53">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK53">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL53">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM53"/>
     </row>
     <row r="54" ht="14.6" customHeight="0">
@@ -6984,9 +7392,21 @@
           <t xml:space="preserve">002</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ54"/>
-      <c s="24" t="str" r="AK54"/>
-      <c s="24" t="str" r="AL54"/>
+      <c s="24" t="inlineStr" r="AJ54">
+        <is>
+          <t xml:space="preserve">002</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK54">
+        <is>
+          <t xml:space="preserve">002</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL54">
+        <is>
+          <t xml:space="preserve">002</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM54"/>
     </row>
     <row r="55" ht="15.3" customHeight="0">
@@ -7118,26 +7538,26 @@
       <c s="13" t="str" r="N57"/>
       <c s="12" t="inlineStr" r="O57">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c s="13" t="str" r="P57"/>
       <c s="13" t="str" r="Q57"/>
       <c s="12" t="inlineStr" r="R57">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c s="13" t="str" r="S57"/>
       <c s="12" t="inlineStr" r="T57">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c s="13" t="str" r="U57"/>
       <c s="12" t="inlineStr" r="V57">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c s="13" t="str" r="W57"/>
@@ -7155,7 +7575,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB57">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c s="13" t="str" r="AC57"/>
@@ -7164,7 +7584,11 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="12" t="str" r="AE57"/>
+      <c s="12" t="inlineStr" r="AE57">
+        <is>
+          <t xml:space="preserve">00:21</t>
+        </is>
+      </c>
       <c s="13" t="str" r="AF57"/>
       <c s="13" t="str" r="AG57"/>
       <c s="12" t="inlineStr" r="AH57">
@@ -7174,11 +7598,7 @@
       </c>
       <c s="12" t="str" r="AI57"/>
       <c s="13" t="str" r="AJ57"/>
-      <c s="12" t="inlineStr" r="AK57">
-        <is>
-          <t xml:space="preserve">00:00</t>
-        </is>
-      </c>
+      <c s="12" t="str" r="AK57"/>
       <c s="13" t="str" r="AL57"/>
       <c s="13" t="str" r="AM57"/>
     </row>
@@ -7188,41 +7608,165 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="15" t="str" r="D58"/>
-      <c s="15" t="str" r="E58"/>
-      <c s="15" t="str" r="F58"/>
-      <c s="15" t="str" r="G58"/>
-      <c s="15" t="str" r="H58"/>
-      <c s="15" t="str" r="I58"/>
-      <c s="15" t="str" r="J58"/>
-      <c s="15" t="str" r="K58"/>
+      <c s="15" t="inlineStr" r="D58">
+        <is>
+          <t xml:space="preserve">01</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="E58">
+        <is>
+          <t xml:space="preserve">02</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="F58">
+        <is>
+          <t xml:space="preserve">03</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="G58">
+        <is>
+          <t xml:space="preserve">04</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="H58">
+        <is>
+          <t xml:space="preserve">05</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="I58">
+        <is>
+          <t xml:space="preserve">06</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="J58">
+        <is>
+          <t xml:space="preserve">07</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="K58">
+        <is>
+          <t xml:space="preserve">08</t>
+        </is>
+      </c>
       <c s="16" t="str" r="L58"/>
-      <c s="15" t="str" r="M58"/>
-      <c s="15" t="str" r="N58"/>
-      <c s="15" t="str" r="O58"/>
+      <c s="15" t="inlineStr" r="M58">
+        <is>
+          <t xml:space="preserve">09</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="N58">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="O58">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
       <c s="16" t="str" r="P58"/>
-      <c s="15" t="str" r="Q58"/>
-      <c s="15" t="str" r="R58"/>
-      <c s="15" t="str" r="S58"/>
-      <c s="15" t="str" r="T58"/>
-      <c s="15" t="str" r="U58"/>
-      <c s="15" t="str" r="V58"/>
-      <c s="15" t="str" r="W58"/>
-      <c s="15" t="str" r="X58"/>
-      <c s="15" t="str" r="Y58"/>
+      <c s="15" t="inlineStr" r="Q58">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="R58">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="S58">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="T58">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="U58">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="V58">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="W58">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="X58">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="Y58">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
       <c s="16" t="str" r="Z58"/>
-      <c s="15" t="str" r="AA58"/>
-      <c s="15" t="str" r="AB58"/>
-      <c s="15" t="str" r="AC58"/>
-      <c s="15" t="str" r="AD58"/>
-      <c s="15" t="str" r="AE58"/>
+      <c s="15" t="inlineStr" r="AA58">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AB58">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AC58">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AD58">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AE58">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AF58"/>
-      <c s="15" t="str" r="AG58"/>
-      <c s="15" t="str" r="AH58"/>
-      <c s="15" t="str" r="AI58"/>
-      <c s="15" t="str" r="AJ58"/>
-      <c s="15" t="str" r="AK58"/>
-      <c s="15" t="str" r="AL58"/>
+      <c s="15" t="inlineStr" r="AG58">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AH58">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AI58">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AJ58">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK58">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL58">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM58"/>
     </row>
     <row r="59" ht="15.35" customHeight="0">
@@ -7375,9 +7919,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ59"/>
-      <c s="18" t="str" r="AK59"/>
-      <c s="20" t="str" r="AL59"/>
+      <c s="18" t="inlineStr" r="AJ59">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK59">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL59">
+        <is>
+          <t xml:space="preserve">12:06</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM59"/>
     </row>
     <row r="60" ht="15.3" customHeight="0">
@@ -7530,9 +8086,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ60"/>
-      <c s="20" t="str" r="AK60"/>
-      <c s="20" t="str" r="AL60"/>
+      <c s="20" t="inlineStr" r="AJ60">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK60">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL60">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM60"/>
     </row>
     <row r="61" ht="15.3" customHeight="0">
@@ -7685,9 +8253,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ61"/>
-      <c s="20" t="str" r="AK61"/>
-      <c s="20" t="str" r="AL61"/>
+      <c s="20" t="inlineStr" r="AJ61">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK61">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL61">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM61"/>
     </row>
     <row r="62" ht="15.35" customHeight="0">
@@ -7840,9 +8420,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ62"/>
-      <c s="20" t="str" r="AK62"/>
-      <c s="20" t="str" r="AL62"/>
+      <c s="20" t="inlineStr" r="AJ62">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK62">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL62">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM62"/>
     </row>
     <row r="63" ht="14.6" customHeight="0">
@@ -7853,151 +8445,163 @@
       </c>
       <c s="20" t="inlineStr" r="D63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="E63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">HLD</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="G63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="H63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">WO</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="I63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="J63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="K63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="21" t="str" r="L63"/>
       <c s="20" t="inlineStr" r="M63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="N63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="O63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="21" t="str" r="P63"/>
       <c s="20" t="inlineStr" r="Q63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">WO</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="R63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="S63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="T63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="V63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="W63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="X63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">WO</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="Y63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="21" t="str" r="Z63"/>
       <c s="20" t="inlineStr" r="AA63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AB63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AC63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AD63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AE63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="21" t="str" r="AF63"/>
       <c s="20" t="inlineStr" r="AG63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">WO</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AH63">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AI63">
         <is>
-          <t xml:space="preserve">00:00</t>
-        </is>
-      </c>
-      <c s="20" t="str" r="AJ63"/>
-      <c s="20" t="str" r="AK63"/>
-      <c s="20" t="str" r="AL63"/>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AJ63">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK63">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL63">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM63"/>
     </row>
     <row r="64" ht="14.6" customHeight="0">
@@ -8006,41 +8610,165 @@
           <t xml:space="preserve">Shift</t>
         </is>
       </c>
-      <c s="24" t="str" r="D64"/>
-      <c s="25" t="str" r="E64"/>
-      <c s="24" t="str" r="F64"/>
-      <c s="24" t="str" r="G64"/>
-      <c s="24" t="str" r="H64"/>
-      <c s="24" t="str" r="I64"/>
-      <c s="24" t="str" r="J64"/>
-      <c s="24" t="str" r="K64"/>
+      <c s="24" t="inlineStr" r="D64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="25" t="inlineStr" r="E64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="F64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="G64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="H64">
+        <is>
+          <t xml:space="preserve">OFF</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="I64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="J64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="K64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="L64"/>
-      <c s="24" t="str" r="M64"/>
-      <c s="24" t="str" r="N64"/>
-      <c s="24" t="str" r="O64"/>
+      <c s="24" t="inlineStr" r="M64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="N64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="O64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="P64"/>
-      <c s="24" t="str" r="Q64"/>
-      <c s="24" t="str" r="R64"/>
-      <c s="24" t="str" r="S64"/>
-      <c s="24" t="str" r="T64"/>
-      <c s="24" t="str" r="U64"/>
-      <c s="24" t="str" r="V64"/>
-      <c s="24" t="str" r="W64"/>
-      <c s="24" t="str" r="X64"/>
-      <c s="24" t="str" r="Y64"/>
+      <c s="24" t="inlineStr" r="Q64">
+        <is>
+          <t xml:space="preserve">OFF</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="R64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="S64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="T64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="U64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="V64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="W64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="X64">
+        <is>
+          <t xml:space="preserve">OFF</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="Y64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="Z64"/>
-      <c s="24" t="str" r="AA64"/>
-      <c s="24" t="str" r="AB64"/>
-      <c s="24" t="str" r="AC64"/>
-      <c s="24" t="str" r="AD64"/>
-      <c s="24" t="str" r="AE64"/>
+      <c s="24" t="inlineStr" r="AA64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AB64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AC64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AD64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AE64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AF64"/>
-      <c s="24" t="str" r="AG64"/>
-      <c s="24" t="str" r="AH64"/>
-      <c s="24" t="str" r="AI64"/>
-      <c s="24" t="str" r="AJ64"/>
-      <c s="24" t="str" r="AK64"/>
-      <c s="24" t="str" r="AL64"/>
+      <c s="24" t="inlineStr" r="AG64">
+        <is>
+          <t xml:space="preserve">OFF</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AH64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AI64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AJ64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL64">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM64"/>
     </row>
     <row r="65" ht="15.3" customHeight="0">
@@ -8466,7 +9194,7 @@
     <row r="1" ht="17" customHeight="0">
       <c s="1" t="inlineStr" r="B1">
         <is>
-          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 28-10-2026</t>
+          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 31-10-2026</t>
         </is>
       </c>
       <c s="2" t="inlineStr" r="P1">
@@ -8476,7 +9204,7 @@
       </c>
       <c s="3" t="inlineStr" r="AF1">
         <is>
-          <t xml:space="preserve">Print Date 28-10-2026</t>
+          <t xml:space="preserve">Print Date 31-10-2026</t>
         </is>
       </c>
     </row>
@@ -8674,7 +9402,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -8693,7 +9421,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -8711,7 +9439,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -8734,13 +9462,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI6">
         <is>
-          <t xml:space="preserve">184:33</t>
+          <t xml:space="preserve">175:8</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ6"/>
       <c s="12" t="inlineStr" r="AK6">
         <is>
-          <t xml:space="preserve">24:58</t>
+          <t xml:space="preserve">15:33</t>
         </is>
       </c>
       <c s="13" t="str" r="AL6"/>
@@ -8896,9 +9624,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ7"/>
-      <c s="15" t="str" r="AK7"/>
-      <c s="15" t="str" r="AL7"/>
+      <c s="15" t="inlineStr" r="AJ7">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK7">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL7">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM7"/>
     </row>
     <row r="8" ht="15.3" customHeight="0">
@@ -8914,7 +9654,7 @@
       </c>
       <c s="18" t="inlineStr" r="E8">
         <is>
-          <t xml:space="preserve">11:15</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="F8">
@@ -9051,9 +9791,21 @@
           <t xml:space="preserve">11:27</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ8"/>
-      <c s="18" t="str" r="AK8"/>
-      <c s="20" t="str" r="AL8"/>
+      <c s="18" t="inlineStr" r="AJ8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL8">
+        <is>
+          <t xml:space="preserve">11:31</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM8"/>
     </row>
     <row r="9" ht="15.3" customHeight="0">
@@ -9069,7 +9821,7 @@
       </c>
       <c s="20" t="inlineStr" r="E9">
         <is>
-          <t xml:space="preserve">20:40</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F9">
@@ -9206,9 +9958,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ9"/>
-      <c s="20" t="str" r="AK9"/>
-      <c s="20" t="str" r="AL9"/>
+      <c s="20" t="inlineStr" r="AJ9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM9"/>
     </row>
     <row r="10" ht="15.35" customHeight="0">
@@ -9224,7 +9988,7 @@
       </c>
       <c s="20" t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">09:25</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F10">
@@ -9361,9 +10125,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ10"/>
-      <c s="20" t="str" r="AK10"/>
-      <c s="20" t="str" r="AL10"/>
+      <c s="20" t="inlineStr" r="AJ10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM10"/>
     </row>
     <row r="11" ht="15.3" customHeight="0">
@@ -9379,7 +10155,7 @@
       </c>
       <c s="20" t="inlineStr" r="E11">
         <is>
-          <t xml:space="preserve">09:25</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F11">
@@ -9516,9 +10292,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ11"/>
-      <c s="20" t="str" r="AK11"/>
-      <c s="20" t="str" r="AL11"/>
+      <c s="20" t="inlineStr" r="AJ11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM11"/>
     </row>
     <row r="12" ht="14.6" customHeight="0">
@@ -9534,7 +10322,7 @@
       </c>
       <c s="20" t="inlineStr" r="E12">
         <is>
-          <t xml:space="preserve">POH</t>
+          <t xml:space="preserve">HLD</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F12">
@@ -9671,9 +10459,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ12"/>
-      <c s="20" t="str" r="AK12"/>
-      <c s="20" t="str" r="AL12"/>
+      <c s="20" t="inlineStr" r="AJ12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL12">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM12"/>
     </row>
     <row r="13" ht="14.6" customHeight="0">
@@ -9826,9 +10626,21 @@
           <t xml:space="preserve">003</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ13"/>
-      <c s="24" t="str" r="AK13"/>
-      <c s="24" t="str" r="AL13"/>
+      <c s="24" t="inlineStr" r="AJ13">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK13">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL13">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM13"/>
     </row>
     <row r="14" ht="15.3" customHeight="0">
@@ -9964,7 +10776,7 @@
     <row r="1" ht="17" customHeight="0">
       <c s="1" t="inlineStr" r="B1">
         <is>
-          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 28-10-2026</t>
+          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 31-10-2026</t>
         </is>
       </c>
       <c s="2" t="inlineStr" r="P1">
@@ -9974,7 +10786,7 @@
       </c>
       <c s="3" t="inlineStr" r="AF1">
         <is>
-          <t xml:space="preserve">Print Date 28-10-2026</t>
+          <t xml:space="preserve">Print Date 31-10-2026</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10984,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -10191,7 +11003,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -10209,7 +11021,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -10220,7 +11032,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE6">
         <is>
-          <t xml:space="preserve">00:44</t>
+          <t xml:space="preserve">1:27</t>
         </is>
       </c>
       <c s="13" t="str" r="AF6"/>
@@ -10394,9 +11206,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ7"/>
-      <c s="15" t="str" r="AK7"/>
-      <c s="15" t="str" r="AL7"/>
+      <c s="15" t="inlineStr" r="AJ7">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK7">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL7">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM7"/>
     </row>
     <row r="8" ht="15.3" customHeight="0">
@@ -10549,9 +11373,21 @@
           <t xml:space="preserve">11:38</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ8"/>
-      <c s="18" t="str" r="AK8"/>
-      <c s="20" t="str" r="AL8"/>
+      <c s="18" t="inlineStr" r="AJ8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL8">
+        <is>
+          <t xml:space="preserve">12:28</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM8"/>
     </row>
     <row r="9" ht="15.3" customHeight="0">
@@ -10704,9 +11540,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ9"/>
-      <c s="20" t="str" r="AK9"/>
-      <c s="20" t="str" r="AL9"/>
+      <c s="20" t="inlineStr" r="AJ9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM9"/>
     </row>
     <row r="10" ht="15.35" customHeight="0">
@@ -10859,9 +11707,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ10"/>
-      <c s="20" t="str" r="AK10"/>
-      <c s="20" t="str" r="AL10"/>
+      <c s="20" t="inlineStr" r="AJ10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM10"/>
     </row>
     <row r="11" ht="15.3" customHeight="0">
@@ -11014,9 +11874,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ11"/>
-      <c s="20" t="str" r="AK11"/>
-      <c s="20" t="str" r="AL11"/>
+      <c s="20" t="inlineStr" r="AJ11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM11"/>
     </row>
     <row r="12" ht="14.6" customHeight="0">
@@ -11169,9 +12041,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ12"/>
-      <c s="20" t="str" r="AK12"/>
-      <c s="20" t="str" r="AL12"/>
+      <c s="20" t="inlineStr" r="AJ12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL12">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM12"/>
     </row>
     <row r="13" ht="14.6" customHeight="0">
@@ -11324,9 +12208,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ13"/>
-      <c s="24" t="str" r="AK13"/>
-      <c s="24" t="str" r="AL13"/>
+      <c s="24" t="inlineStr" r="AJ13">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK13">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL13">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM13"/>
     </row>
     <row r="14" ht="15.3" customHeight="0">
@@ -11458,7 +12354,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -11477,7 +12373,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -11495,7 +12391,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -11506,7 +12402,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE16">
         <is>
-          <t xml:space="preserve">9:38</t>
+          <t xml:space="preserve">10:20</t>
         </is>
       </c>
       <c s="13" t="str" r="AF16"/>
@@ -11680,9 +12576,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ17"/>
-      <c s="15" t="str" r="AK17"/>
-      <c s="15" t="str" r="AL17"/>
+      <c s="15" t="inlineStr" r="AJ17">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK17">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL17">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM17"/>
     </row>
     <row r="18" ht="15.35" customHeight="0">
@@ -11835,9 +12743,21 @@
           <t xml:space="preserve">11:55</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ18"/>
-      <c s="18" t="str" r="AK18"/>
-      <c s="20" t="str" r="AL18"/>
+      <c s="18" t="inlineStr" r="AJ18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL18">
+        <is>
+          <t xml:space="preserve">12:27</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM18"/>
     </row>
     <row r="19" ht="15.3" customHeight="0">
@@ -11990,9 +12910,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ19"/>
-      <c s="20" t="str" r="AK19"/>
-      <c s="20" t="str" r="AL19"/>
+      <c s="20" t="inlineStr" r="AJ19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM19"/>
     </row>
     <row r="20" ht="15.35" customHeight="0">
@@ -12145,9 +13077,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ20"/>
-      <c s="20" t="str" r="AK20"/>
-      <c s="20" t="str" r="AL20"/>
+      <c s="20" t="inlineStr" r="AJ20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM20"/>
     </row>
     <row r="21" ht="15.3" customHeight="0">
@@ -12300,9 +13244,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ21"/>
-      <c s="20" t="str" r="AK21"/>
-      <c s="20" t="str" r="AL21"/>
+      <c s="20" t="inlineStr" r="AJ21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM21"/>
     </row>
     <row r="22" ht="14.6" customHeight="0">
@@ -12455,9 +13411,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ22"/>
-      <c s="20" t="str" r="AK22"/>
-      <c s="20" t="str" r="AL22"/>
+      <c s="20" t="inlineStr" r="AJ22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL22">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM22"/>
     </row>
     <row r="23" ht="14.6" customHeight="0">
@@ -12610,9 +13578,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ23"/>
-      <c s="24" t="str" r="AK23"/>
-      <c s="24" t="str" r="AL23"/>
+      <c s="24" t="inlineStr" r="AJ23">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK23">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL23">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM23"/>
     </row>
     <row r="24" ht="15.3" customHeight="0">
@@ -12806,7 +13786,7 @@
     <row r="1" ht="17" customHeight="0">
       <c s="1" t="inlineStr" r="B1">
         <is>
-          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 28-10-2026</t>
+          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 31-10-2026</t>
         </is>
       </c>
       <c s="2" t="inlineStr" r="P1">
@@ -12816,7 +13796,7 @@
       </c>
       <c s="3" t="inlineStr" r="AF1">
         <is>
-          <t xml:space="preserve">Print Date 28-10-2026</t>
+          <t xml:space="preserve">Print Date 31-10-2026</t>
         </is>
       </c>
     </row>
@@ -13033,7 +14013,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -13167,9 +14147,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="W7"/>
-      <c s="15" t="str" r="X7"/>
-      <c s="15" t="str" r="Y7"/>
+      <c s="15" t="inlineStr" r="W7">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="X7">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="Y7">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="Z7"/>
       <c s="15" t="str" r="AA7"/>
       <c s="15" t="str" r="AB7"/>
@@ -13335,9 +14327,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ8"/>
-      <c s="18" t="str" r="AK8"/>
-      <c s="20" t="str" r="AL8"/>
+      <c s="18" t="inlineStr" r="AJ8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM8"/>
     </row>
     <row r="9" ht="15.3" customHeight="0">
@@ -13490,9 +14494,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ9"/>
-      <c s="20" t="str" r="AK9"/>
-      <c s="20" t="str" r="AL9"/>
+      <c s="20" t="inlineStr" r="AJ9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM9"/>
     </row>
     <row r="10" ht="15.35" customHeight="0">
@@ -13645,9 +14661,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ10"/>
-      <c s="20" t="str" r="AK10"/>
-      <c s="20" t="str" r="AL10"/>
+      <c s="20" t="inlineStr" r="AJ10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM10"/>
     </row>
     <row r="11" ht="15.3" customHeight="0">
@@ -13800,9 +14828,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ11"/>
-      <c s="20" t="str" r="AK11"/>
-      <c s="20" t="str" r="AL11"/>
+      <c s="20" t="inlineStr" r="AJ11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM11"/>
     </row>
     <row r="12" ht="14.6" customHeight="0">
@@ -13900,17 +14940,17 @@
       </c>
       <c s="20" t="inlineStr" r="W12">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="X12">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="Y12">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="21" t="str" r="Z12"/>
@@ -13955,9 +14995,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ12"/>
-      <c s="20" t="str" r="AK12"/>
-      <c s="20" t="str" r="AL12"/>
+      <c s="20" t="inlineStr" r="AJ12">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK12">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL12">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM12"/>
     </row>
     <row r="13" ht="14.6" customHeight="0">
@@ -14053,9 +15105,21 @@
           <t xml:space="preserve">003</t>
         </is>
       </c>
-      <c s="24" t="str" r="W13"/>
-      <c s="24" t="str" r="X13"/>
-      <c s="24" t="str" r="Y13"/>
+      <c s="24" t="inlineStr" r="W13">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="X13">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="Y13">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
       <c s="26" t="str" r="Z13"/>
       <c s="24" t="str" r="AA13"/>
       <c s="24" t="str" r="AB13"/>
@@ -14204,7 +15268,7 @@
     <row r="1" ht="17" customHeight="0">
       <c s="1" t="inlineStr" r="B1">
         <is>
-          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 28-10-2026</t>
+          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 31-10-2026</t>
         </is>
       </c>
       <c s="2" t="inlineStr" r="P1">
@@ -14214,7 +15278,7 @@
       </c>
       <c s="3" t="inlineStr" r="AF1">
         <is>
-          <t xml:space="preserve">Print Date 28-10-2026</t>
+          <t xml:space="preserve">Print Date 31-10-2026</t>
         </is>
       </c>
     </row>
@@ -14412,7 +15476,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -14431,7 +15495,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -14449,7 +15513,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -14460,7 +15524,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE6">
         <is>
-          <t xml:space="preserve">7:21</t>
+          <t xml:space="preserve">7:43</t>
         </is>
       </c>
       <c s="13" t="str" r="AF6"/>
@@ -14472,13 +15536,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI6">
         <is>
-          <t xml:space="preserve">198:28</t>
+          <t xml:space="preserve">189:7</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ6"/>
       <c s="12" t="inlineStr" r="AK6">
         <is>
-          <t xml:space="preserve">22:33</t>
+          <t xml:space="preserve">13:12</t>
         </is>
       </c>
       <c s="13" t="str" r="AL6"/>
@@ -14634,9 +15698,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ7"/>
-      <c s="15" t="str" r="AK7"/>
-      <c s="15" t="str" r="AL7"/>
+      <c s="15" t="inlineStr" r="AJ7">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK7">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL7">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM7"/>
     </row>
     <row r="8" ht="15.3" customHeight="0">
@@ -14652,7 +15728,7 @@
       </c>
       <c s="18" t="inlineStr" r="E8">
         <is>
-          <t xml:space="preserve">11:38</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="F8">
@@ -14789,9 +15865,21 @@
           <t xml:space="preserve">12:20</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ8"/>
-      <c s="18" t="str" r="AK8"/>
-      <c s="20" t="str" r="AL8"/>
+      <c s="18" t="inlineStr" r="AJ8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL8">
+        <is>
+          <t xml:space="preserve">11:52</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM8"/>
     </row>
     <row r="9" ht="15.3" customHeight="0">
@@ -14807,7 +15895,7 @@
       </c>
       <c s="20" t="inlineStr" r="E9">
         <is>
-          <t xml:space="preserve">20:59</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F9">
@@ -14944,9 +16032,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ9"/>
-      <c s="20" t="str" r="AK9"/>
-      <c s="20" t="str" r="AL9"/>
+      <c s="20" t="inlineStr" r="AJ9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM9"/>
     </row>
     <row r="10" ht="15.35" customHeight="0">
@@ -14962,7 +16062,7 @@
       </c>
       <c s="20" t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">09:21</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F10">
@@ -15099,9 +16199,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ10"/>
-      <c s="20" t="str" r="AK10"/>
-      <c s="20" t="str" r="AL10"/>
+      <c s="20" t="inlineStr" r="AJ10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM10"/>
     </row>
     <row r="11" ht="15.3" customHeight="0">
@@ -15117,7 +16229,7 @@
       </c>
       <c s="20" t="inlineStr" r="E11">
         <is>
-          <t xml:space="preserve">09:21</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F11">
@@ -15254,9 +16366,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ11"/>
-      <c s="20" t="str" r="AK11"/>
-      <c s="20" t="str" r="AL11"/>
+      <c s="20" t="inlineStr" r="AJ11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM11"/>
     </row>
     <row r="12" ht="14.6" customHeight="0">
@@ -15272,7 +16396,7 @@
       </c>
       <c s="20" t="inlineStr" r="E12">
         <is>
-          <t xml:space="preserve">POH</t>
+          <t xml:space="preserve">HLD</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F12">
@@ -15409,9 +16533,21 @@
           <t xml:space="preserve">P/2</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ12"/>
-      <c s="20" t="str" r="AK12"/>
-      <c s="20" t="str" r="AL12"/>
+      <c s="20" t="inlineStr" r="AJ12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL12">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM12"/>
     </row>
     <row r="13" ht="14.6" customHeight="0">
@@ -15564,9 +16700,21 @@
           <t xml:space="preserve">003</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ13"/>
-      <c s="24" t="str" r="AK13"/>
-      <c s="24" t="str" r="AL13"/>
+      <c s="24" t="inlineStr" r="AJ13">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK13">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL13">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM13"/>
     </row>
     <row r="14" ht="15.3" customHeight="0">
@@ -15698,7 +16846,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -15717,7 +16865,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -15735,7 +16883,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -15758,7 +16906,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI16">
         <is>
-          <t xml:space="preserve">84:25</t>
+          <t xml:space="preserve">85:38</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ16"/>
@@ -15916,9 +17064,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ17"/>
-      <c s="15" t="str" r="AK17"/>
-      <c s="15" t="str" r="AL17"/>
+      <c s="15" t="inlineStr" r="AJ17">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK17">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL17">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM17"/>
     </row>
     <row r="18" ht="15.35" customHeight="0">
@@ -16071,9 +17231,21 @@
           <t xml:space="preserve">11:25</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ18"/>
-      <c s="18" t="str" r="AK18"/>
-      <c s="20" t="str" r="AL18"/>
+      <c s="18" t="inlineStr" r="AJ18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL18">
+        <is>
+          <t xml:space="preserve">11:08</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM18"/>
     </row>
     <row r="19" ht="15.3" customHeight="0">
@@ -16226,9 +17398,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ19"/>
-      <c s="20" t="str" r="AK19"/>
-      <c s="20" t="str" r="AL19"/>
+      <c s="20" t="inlineStr" r="AJ19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL19">
+        <is>
+          <t xml:space="preserve">12:21</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM19"/>
     </row>
     <row r="20" ht="15.35" customHeight="0">
@@ -16381,9 +17565,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ20"/>
-      <c s="20" t="str" r="AK20"/>
-      <c s="20" t="str" r="AL20"/>
+      <c s="20" t="inlineStr" r="AJ20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL20">
+        <is>
+          <t xml:space="preserve">01:13</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM20"/>
     </row>
     <row r="21" ht="15.3" customHeight="0">
@@ -16536,9 +17732,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ21"/>
-      <c s="20" t="str" r="AK21"/>
-      <c s="20" t="str" r="AL21"/>
+      <c s="20" t="inlineStr" r="AJ21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM21"/>
     </row>
     <row r="22" ht="14.6" customHeight="0">
@@ -16691,9 +17899,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ22"/>
-      <c s="20" t="str" r="AK22"/>
-      <c s="20" t="str" r="AL22"/>
+      <c s="20" t="inlineStr" r="AJ22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL22">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM22"/>
     </row>
     <row r="23" ht="14.6" customHeight="0">
@@ -16846,9 +18066,21 @@
           <t xml:space="preserve">002</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ23"/>
-      <c s="24" t="str" r="AK23"/>
-      <c s="24" t="str" r="AL23"/>
+      <c s="24" t="inlineStr" r="AJ23">
+        <is>
+          <t xml:space="preserve">002</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK23">
+        <is>
+          <t xml:space="preserve">002</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL23">
+        <is>
+          <t xml:space="preserve">002</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM23"/>
     </row>
     <row r="24" ht="15.3" customHeight="0">
@@ -16980,7 +18212,7 @@
       <c s="13" t="str" r="N26"/>
       <c s="12" t="inlineStr" r="O26">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c s="13" t="str" r="P26"/>
@@ -16999,7 +18231,7 @@
       <c s="13" t="str" r="U26"/>
       <c s="12" t="inlineStr" r="V26">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c s="13" t="str" r="W26"/>
@@ -17017,7 +18249,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB26">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c s="13" t="str" r="AC26"/>
@@ -17028,7 +18260,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE26">
         <is>
-          <t xml:space="preserve">22:52</t>
+          <t xml:space="preserve">23:12</t>
         </is>
       </c>
       <c s="13" t="str" r="AF26"/>
@@ -17202,9 +18434,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ27"/>
-      <c s="15" t="str" r="AK27"/>
-      <c s="15" t="str" r="AL27"/>
+      <c s="15" t="inlineStr" r="AJ27">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK27">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL27">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM27"/>
     </row>
     <row r="28" ht="15.35" customHeight="0">
@@ -17357,9 +18601,21 @@
           <t xml:space="preserve">12:16</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ28"/>
-      <c s="18" t="str" r="AK28"/>
-      <c s="20" t="str" r="AL28"/>
+      <c s="18" t="inlineStr" r="AJ28">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK28">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL28">
+        <is>
+          <t xml:space="preserve">12:05</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM28"/>
     </row>
     <row r="29" ht="15.3" customHeight="0">
@@ -17512,9 +18768,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ29"/>
-      <c s="20" t="str" r="AK29"/>
-      <c s="20" t="str" r="AL29"/>
+      <c s="20" t="inlineStr" r="AJ29">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK29">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL29">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM29"/>
     </row>
     <row r="30" ht="15.35" customHeight="0">
@@ -17667,9 +18935,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ30"/>
-      <c s="20" t="str" r="AK30"/>
-      <c s="20" t="str" r="AL30"/>
+      <c s="20" t="inlineStr" r="AJ30">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK30">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL30">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM30"/>
     </row>
     <row r="31" ht="15.3" customHeight="0">
@@ -17822,9 +19102,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ31"/>
-      <c s="20" t="str" r="AK31"/>
-      <c s="20" t="str" r="AL31"/>
+      <c s="20" t="inlineStr" r="AJ31">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK31">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL31">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM31"/>
     </row>
     <row r="32" ht="14.6" customHeight="0">
@@ -17977,9 +19269,21 @@
           <t xml:space="preserve">P-LT</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ32"/>
-      <c s="20" t="str" r="AK32"/>
-      <c s="20" t="str" r="AL32"/>
+      <c s="20" t="inlineStr" r="AJ32">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK32">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL32">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM32"/>
     </row>
     <row r="33" ht="14.6" customHeight="0">
@@ -18132,9 +19436,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ33"/>
-      <c s="24" t="str" r="AK33"/>
-      <c s="24" t="str" r="AL33"/>
+      <c s="24" t="inlineStr" r="AJ33">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK33">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL33">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM33"/>
     </row>
     <row r="34" ht="15.3" customHeight="0">
@@ -18266,7 +19582,7 @@
       <c s="13" t="str" r="N36"/>
       <c s="12" t="inlineStr" r="O36">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c s="13" t="str" r="P36"/>
@@ -18285,7 +19601,7 @@
       <c s="13" t="str" r="U36"/>
       <c s="12" t="inlineStr" r="V36">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c s="13" t="str" r="W36"/>
@@ -18303,7 +19619,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB36">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c s="13" t="str" r="AC36"/>
@@ -18326,13 +19642,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI36">
         <is>
-          <t xml:space="preserve">190:12</t>
+          <t xml:space="preserve">181:3</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ36"/>
       <c s="12" t="inlineStr" r="AK36">
         <is>
-          <t xml:space="preserve">21:27</t>
+          <t xml:space="preserve">12:18</t>
         </is>
       </c>
       <c s="13" t="str" r="AL36"/>
@@ -18488,9 +19804,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ37"/>
-      <c s="15" t="str" r="AK37"/>
-      <c s="15" t="str" r="AL37"/>
+      <c s="15" t="inlineStr" r="AJ37">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK37">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL37">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM37"/>
     </row>
     <row r="38" ht="15.35" customHeight="0">
@@ -18506,7 +19834,7 @@
       </c>
       <c s="18" t="inlineStr" r="E38">
         <is>
-          <t xml:space="preserve">11:23</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="F38">
@@ -18643,9 +19971,21 @@
           <t xml:space="preserve">11:27</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ38"/>
-      <c s="18" t="str" r="AK38"/>
-      <c s="20" t="str" r="AL38"/>
+      <c s="18" t="inlineStr" r="AJ38">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK38">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL38">
+        <is>
+          <t xml:space="preserve">11:22</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM38"/>
     </row>
     <row r="39" ht="15.3" customHeight="0">
@@ -18661,7 +20001,7 @@
       </c>
       <c s="20" t="inlineStr" r="E39">
         <is>
-          <t xml:space="preserve">20:32</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F39">
@@ -18798,9 +20138,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ39"/>
-      <c s="20" t="str" r="AK39"/>
-      <c s="20" t="str" r="AL39"/>
+      <c s="20" t="inlineStr" r="AJ39">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK39">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL39">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM39"/>
     </row>
     <row r="40" ht="15.3" customHeight="0">
@@ -18816,7 +20168,7 @@
       </c>
       <c s="20" t="inlineStr" r="E40">
         <is>
-          <t xml:space="preserve">09:09</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F40">
@@ -18953,9 +20305,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ40"/>
-      <c s="20" t="str" r="AK40"/>
-      <c s="20" t="str" r="AL40"/>
+      <c s="20" t="inlineStr" r="AJ40">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK40">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL40">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM40"/>
     </row>
     <row r="41" ht="15.35" customHeight="0">
@@ -18971,7 +20335,7 @@
       </c>
       <c s="20" t="inlineStr" r="E41">
         <is>
-          <t xml:space="preserve">09:09</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F41">
@@ -19108,9 +20472,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ41"/>
-      <c s="20" t="str" r="AK41"/>
-      <c s="20" t="str" r="AL41"/>
+      <c s="20" t="inlineStr" r="AJ41">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK41">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL41">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM41"/>
     </row>
     <row r="42" ht="14.6" customHeight="0">
@@ -19126,7 +20502,7 @@
       </c>
       <c s="20" t="inlineStr" r="E42">
         <is>
-          <t xml:space="preserve">POH</t>
+          <t xml:space="preserve">HLD</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F42">
@@ -19263,9 +20639,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ42"/>
-      <c s="20" t="str" r="AK42"/>
-      <c s="20" t="str" r="AL42"/>
+      <c s="20" t="inlineStr" r="AJ42">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK42">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL42">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM42"/>
     </row>
     <row r="43" ht="14.6" customHeight="0">
@@ -19418,9 +20806,21 @@
           <t xml:space="preserve">003</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ43"/>
-      <c s="24" t="str" r="AK43"/>
-      <c s="24" t="str" r="AL43"/>
+      <c s="24" t="inlineStr" r="AJ43">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK43">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL43">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM43"/>
     </row>
     <row r="44" ht="15.3" customHeight="0">
@@ -19730,7 +21130,7 @@
     <row r="1" ht="17" customHeight="0">
       <c s="1" t="inlineStr" r="B1">
         <is>
-          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 28-10-2026</t>
+          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 31-10-2026</t>
         </is>
       </c>
       <c s="2" t="inlineStr" r="P1">
@@ -19740,7 +21140,7 @@
       </c>
       <c s="3" t="inlineStr" r="AF1">
         <is>
-          <t xml:space="preserve">Print Date 28-10-2026</t>
+          <t xml:space="preserve">Print Date 31-10-2026</t>
         </is>
       </c>
     </row>
@@ -19938,7 +21338,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -19957,7 +21357,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -19975,7 +21375,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -19986,7 +21386,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE6">
         <is>
-          <t xml:space="preserve">7:24</t>
+          <t xml:space="preserve">8:17</t>
         </is>
       </c>
       <c s="13" t="str" r="AF6"/>
@@ -20160,9 +21560,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ7"/>
-      <c s="15" t="str" r="AK7"/>
-      <c s="15" t="str" r="AL7"/>
+      <c s="15" t="inlineStr" r="AJ7">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK7">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL7">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM7"/>
     </row>
     <row r="8" ht="15.3" customHeight="0">
@@ -20315,9 +21727,21 @@
           <t xml:space="preserve">12:55</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ8"/>
-      <c s="18" t="str" r="AK8"/>
-      <c s="20" t="str" r="AL8"/>
+      <c s="18" t="inlineStr" r="AJ8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL8">
+        <is>
+          <t xml:space="preserve">12:38</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM8"/>
     </row>
     <row r="9" ht="15.3" customHeight="0">
@@ -20470,9 +21894,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ9"/>
-      <c s="20" t="str" r="AK9"/>
-      <c s="20" t="str" r="AL9"/>
+      <c s="20" t="inlineStr" r="AJ9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM9"/>
     </row>
     <row r="10" ht="15.35" customHeight="0">
@@ -20625,9 +22061,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ10"/>
-      <c s="20" t="str" r="AK10"/>
-      <c s="20" t="str" r="AL10"/>
+      <c s="20" t="inlineStr" r="AJ10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM10"/>
     </row>
     <row r="11" ht="15.3" customHeight="0">
@@ -20780,9 +22228,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ11"/>
-      <c s="20" t="str" r="AK11"/>
-      <c s="20" t="str" r="AL11"/>
+      <c s="20" t="inlineStr" r="AJ11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM11"/>
     </row>
     <row r="12" ht="14.6" customHeight="0">
@@ -20935,9 +22395,21 @@
           <t xml:space="preserve">P-LT</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ12"/>
-      <c s="20" t="str" r="AK12"/>
-      <c s="20" t="str" r="AL12"/>
+      <c s="20" t="inlineStr" r="AJ12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL12">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM12"/>
     </row>
     <row r="13" ht="14.6" customHeight="0">
@@ -21090,9 +22562,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ13"/>
-      <c s="24" t="str" r="AK13"/>
-      <c s="24" t="str" r="AL13"/>
+      <c s="24" t="inlineStr" r="AJ13">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK13">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL13">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM13"/>
     </row>
     <row r="14" ht="15.3" customHeight="0">
@@ -21224,7 +22708,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -21243,7 +22727,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -21261,7 +22745,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -21446,9 +22930,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ17"/>
-      <c s="15" t="str" r="AK17"/>
-      <c s="15" t="str" r="AL17"/>
+      <c s="15" t="inlineStr" r="AJ17">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK17">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL17">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM17"/>
     </row>
     <row r="18" ht="15.35" customHeight="0">
@@ -21601,9 +23097,21 @@
           <t xml:space="preserve">11:25</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ18"/>
-      <c s="18" t="str" r="AK18"/>
-      <c s="20" t="str" r="AL18"/>
+      <c s="18" t="inlineStr" r="AJ18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL18">
+        <is>
+          <t xml:space="preserve">11:08</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM18"/>
     </row>
     <row r="19" ht="15.3" customHeight="0">
@@ -21756,9 +23264,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ19"/>
-      <c s="20" t="str" r="AK19"/>
-      <c s="20" t="str" r="AL19"/>
+      <c s="20" t="inlineStr" r="AJ19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM19"/>
     </row>
     <row r="20" ht="15.35" customHeight="0">
@@ -21911,9 +23431,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ20"/>
-      <c s="20" t="str" r="AK20"/>
-      <c s="20" t="str" r="AL20"/>
+      <c s="20" t="inlineStr" r="AJ20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM20"/>
     </row>
     <row r="21" ht="15.3" customHeight="0">
@@ -22066,9 +23598,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ21"/>
-      <c s="20" t="str" r="AK21"/>
-      <c s="20" t="str" r="AL21"/>
+      <c s="20" t="inlineStr" r="AJ21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM21"/>
     </row>
     <row r="22" ht="14.6" customHeight="0">
@@ -22221,9 +23765,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ22"/>
-      <c s="20" t="str" r="AK22"/>
-      <c s="20" t="str" r="AL22"/>
+      <c s="20" t="inlineStr" r="AJ22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL22">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM22"/>
     </row>
     <row r="23" ht="14.6" customHeight="0">
@@ -22376,9 +23932,21 @@
           <t xml:space="preserve">002</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ23"/>
-      <c s="24" t="str" r="AK23"/>
-      <c s="24" t="str" r="AL23"/>
+      <c s="24" t="inlineStr" r="AJ23">
+        <is>
+          <t xml:space="preserve">002</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK23">
+        <is>
+          <t xml:space="preserve">002</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL23">
+        <is>
+          <t xml:space="preserve">002</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM23"/>
     </row>
     <row r="24" ht="15.3" customHeight="0">
@@ -22510,7 +24078,7 @@
       <c s="13" t="str" r="N26"/>
       <c s="12" t="inlineStr" r="O26">
         <is>
-          <t xml:space="preserve">21.5</t>
+          <t xml:space="preserve">22.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P26"/>
@@ -22529,7 +24097,7 @@
       <c s="13" t="str" r="U26"/>
       <c s="12" t="inlineStr" r="V26">
         <is>
-          <t xml:space="preserve">1.5</t>
+          <t xml:space="preserve">3.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W26"/>
@@ -22547,7 +24115,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB26">
         <is>
-          <t xml:space="preserve">26.5</t>
+          <t xml:space="preserve">27.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC26"/>
@@ -22732,9 +24300,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ27"/>
-      <c s="15" t="str" r="AK27"/>
-      <c s="15" t="str" r="AL27"/>
+      <c s="15" t="inlineStr" r="AJ27">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK27">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL27">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM27"/>
     </row>
     <row r="28" ht="15.35" customHeight="0">
@@ -22887,9 +24467,21 @@
           <t xml:space="preserve">11:41</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ28"/>
-      <c s="18" t="str" r="AK28"/>
-      <c s="20" t="str" r="AL28"/>
+      <c s="18" t="inlineStr" r="AJ28">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK28">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL28">
+        <is>
+          <t xml:space="preserve">11:29</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM28"/>
     </row>
     <row r="29" ht="15.3" customHeight="0">
@@ -23042,9 +24634,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ29"/>
-      <c s="20" t="str" r="AK29"/>
-      <c s="20" t="str" r="AL29"/>
+      <c s="20" t="inlineStr" r="AJ29">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK29">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL29">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM29"/>
     </row>
     <row r="30" ht="15.35" customHeight="0">
@@ -23197,9 +24801,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ30"/>
-      <c s="20" t="str" r="AK30"/>
-      <c s="20" t="str" r="AL30"/>
+      <c s="20" t="inlineStr" r="AJ30">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK30">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL30">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM30"/>
     </row>
     <row r="31" ht="15.3" customHeight="0">
@@ -23352,9 +24968,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ31"/>
-      <c s="20" t="str" r="AK31"/>
-      <c s="20" t="str" r="AL31"/>
+      <c s="20" t="inlineStr" r="AJ31">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK31">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL31">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM31"/>
     </row>
     <row r="32" ht="14.6" customHeight="0">
@@ -23507,9 +25135,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ32"/>
-      <c s="20" t="str" r="AK32"/>
-      <c s="20" t="str" r="AL32"/>
+      <c s="20" t="inlineStr" r="AJ32">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK32">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL32">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM32"/>
     </row>
     <row r="33" ht="14.6" customHeight="0">
@@ -23662,9 +25302,21 @@
           <t xml:space="preserve">003</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ33"/>
-      <c s="24" t="str" r="AK33"/>
-      <c s="24" t="str" r="AL33"/>
+      <c s="24" t="inlineStr" r="AJ33">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK33">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL33">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM33"/>
     </row>
     <row r="34" ht="15.3" customHeight="0">
@@ -23796,7 +25448,7 @@
       <c s="13" t="str" r="N36"/>
       <c s="12" t="inlineStr" r="O36">
         <is>
-          <t xml:space="preserve">18.5</t>
+          <t xml:space="preserve">19.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P36"/>
@@ -23815,7 +25467,7 @@
       <c s="13" t="str" r="U36"/>
       <c s="12" t="inlineStr" r="V36">
         <is>
-          <t xml:space="preserve">4.5</t>
+          <t xml:space="preserve">6.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W36"/>
@@ -23833,7 +25485,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB36">
         <is>
-          <t xml:space="preserve">23.5</t>
+          <t xml:space="preserve">24.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC36"/>
@@ -23844,7 +25496,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE36">
         <is>
-          <t xml:space="preserve">11:51</t>
+          <t xml:space="preserve">13:51</t>
         </is>
       </c>
       <c s="13" t="str" r="AF36"/>
@@ -24018,9 +25670,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ37"/>
-      <c s="15" t="str" r="AK37"/>
-      <c s="15" t="str" r="AL37"/>
+      <c s="15" t="inlineStr" r="AJ37">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK37">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL37">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM37"/>
     </row>
     <row r="38" ht="15.35" customHeight="0">
@@ -24173,9 +25837,21 @@
           <t xml:space="preserve">12:11</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ38"/>
-      <c s="18" t="str" r="AK38"/>
-      <c s="20" t="str" r="AL38"/>
+      <c s="18" t="inlineStr" r="AJ38">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK38">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL38">
+        <is>
+          <t xml:space="preserve">13:30</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM38"/>
     </row>
     <row r="39" ht="15.3" customHeight="0">
@@ -24328,9 +26004,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ39"/>
-      <c s="20" t="str" r="AK39"/>
-      <c s="20" t="str" r="AL39"/>
+      <c s="20" t="inlineStr" r="AJ39">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK39">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL39">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM39"/>
     </row>
     <row r="40" ht="15.3" customHeight="0">
@@ -24483,9 +26171,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ40"/>
-      <c s="20" t="str" r="AK40"/>
-      <c s="20" t="str" r="AL40"/>
+      <c s="20" t="inlineStr" r="AJ40">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK40">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL40">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM40"/>
     </row>
     <row r="41" ht="15.35" customHeight="0">
@@ -24638,9 +26338,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ41"/>
-      <c s="20" t="str" r="AK41"/>
-      <c s="20" t="str" r="AL41"/>
+      <c s="20" t="inlineStr" r="AJ41">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK41">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL41">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM41"/>
     </row>
     <row r="42" ht="14.6" customHeight="0">
@@ -24793,9 +26505,21 @@
           <t xml:space="preserve">P-LT</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ42"/>
-      <c s="20" t="str" r="AK42"/>
-      <c s="20" t="str" r="AL42"/>
+      <c s="20" t="inlineStr" r="AJ42">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK42">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL42">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM42"/>
     </row>
     <row r="43" ht="14.6" customHeight="0">
@@ -24948,9 +26672,21 @@
           <t xml:space="preserve">003</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ43"/>
-      <c s="24" t="str" r="AK43"/>
-      <c s="24" t="str" r="AL43"/>
+      <c s="24" t="inlineStr" r="AJ43">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK43">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL43">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM43"/>
     </row>
     <row r="44" ht="15.3" customHeight="0">
@@ -25082,7 +26818,7 @@
       <c s="13" t="str" r="N46"/>
       <c s="12" t="inlineStr" r="O46">
         <is>
-          <t xml:space="preserve">20.5</t>
+          <t xml:space="preserve">21.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P46"/>
@@ -25101,7 +26837,7 @@
       <c s="13" t="str" r="U46"/>
       <c s="12" t="inlineStr" r="V46">
         <is>
-          <t xml:space="preserve">2.5</t>
+          <t xml:space="preserve">4.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W46"/>
@@ -25119,7 +26855,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB46">
         <is>
-          <t xml:space="preserve">25.5</t>
+          <t xml:space="preserve">26.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC46"/>
@@ -25130,7 +26866,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE46">
         <is>
-          <t xml:space="preserve">4:46</t>
+          <t xml:space="preserve">5:39</t>
         </is>
       </c>
       <c s="13" t="str" r="AF46"/>
@@ -25142,13 +26878,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI46">
         <is>
-          <t xml:space="preserve">184:14</t>
+          <t xml:space="preserve">174:54</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ46"/>
       <c s="12" t="inlineStr" r="AK46">
         <is>
-          <t xml:space="preserve">23:39</t>
+          <t xml:space="preserve">14:19</t>
         </is>
       </c>
       <c s="13" t="str" r="AL46"/>
@@ -25304,9 +27040,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ47"/>
-      <c s="15" t="str" r="AK47"/>
-      <c s="15" t="str" r="AL47"/>
+      <c s="15" t="inlineStr" r="AJ47">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK47">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL47">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM47"/>
     </row>
     <row r="48" ht="15.35" customHeight="0">
@@ -25322,7 +27070,7 @@
       </c>
       <c s="18" t="inlineStr" r="E48">
         <is>
-          <t xml:space="preserve">11:40</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="F48">
@@ -25459,9 +27207,21 @@
           <t xml:space="preserve">12:26</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ48"/>
-      <c s="18" t="str" r="AK48"/>
-      <c s="20" t="str" r="AL48"/>
+      <c s="18" t="inlineStr" r="AJ48">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK48">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL48">
+        <is>
+          <t xml:space="preserve">12:38</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM48"/>
     </row>
     <row r="49" ht="15.3" customHeight="0">
@@ -25477,7 +27237,7 @@
       </c>
       <c s="20" t="inlineStr" r="E49">
         <is>
-          <t xml:space="preserve">21:00</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F49">
@@ -25614,9 +27374,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ49"/>
-      <c s="20" t="str" r="AK49"/>
-      <c s="20" t="str" r="AL49"/>
+      <c s="20" t="inlineStr" r="AJ49">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK49">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL49">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM49"/>
     </row>
     <row r="50" ht="15.3" customHeight="0">
@@ -25632,7 +27404,7 @@
       </c>
       <c s="20" t="inlineStr" r="E50">
         <is>
-          <t xml:space="preserve">09:20</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F50">
@@ -25769,9 +27541,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ50"/>
-      <c s="20" t="str" r="AK50"/>
-      <c s="20" t="str" r="AL50"/>
+      <c s="20" t="inlineStr" r="AJ50">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK50">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL50">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM50"/>
     </row>
     <row r="51" ht="15.35" customHeight="0">
@@ -25787,7 +27571,7 @@
       </c>
       <c s="20" t="inlineStr" r="E51">
         <is>
-          <t xml:space="preserve">09:20</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F51">
@@ -25924,9 +27708,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ51"/>
-      <c s="20" t="str" r="AK51"/>
-      <c s="20" t="str" r="AL51"/>
+      <c s="20" t="inlineStr" r="AJ51">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK51">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL51">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM51"/>
     </row>
     <row r="52" ht="14.6" customHeight="0">
@@ -25942,7 +27738,7 @@
       </c>
       <c s="20" t="inlineStr" r="E52">
         <is>
-          <t xml:space="preserve">POH</t>
+          <t xml:space="preserve">HLD</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F52">
@@ -26079,9 +27875,21 @@
           <t xml:space="preserve">P-LT</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ52"/>
-      <c s="20" t="str" r="AK52"/>
-      <c s="20" t="str" r="AL52"/>
+      <c s="20" t="inlineStr" r="AJ52">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK52">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL52">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM52"/>
     </row>
     <row r="53" ht="14.6" customHeight="0">
@@ -26234,9 +28042,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ53"/>
-      <c s="24" t="str" r="AK53"/>
-      <c s="24" t="str" r="AL53"/>
+      <c s="24" t="inlineStr" r="AJ53">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK53">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL53">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM53"/>
     </row>
     <row r="54" ht="15.3" customHeight="0">
@@ -26368,7 +28188,7 @@
       <c s="13" t="str" r="N56"/>
       <c s="12" t="inlineStr" r="O56">
         <is>
-          <t xml:space="preserve">15.5</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c s="13" t="str" r="P56"/>
@@ -26387,7 +28207,7 @@
       <c s="13" t="str" r="U56"/>
       <c s="12" t="inlineStr" r="V56">
         <is>
-          <t xml:space="preserve">7.5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="13" t="str" r="W56"/>
@@ -26405,7 +28225,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB56">
         <is>
-          <t xml:space="preserve">20.5</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c s="13" t="str" r="AC56"/>
@@ -26416,7 +28236,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE56">
         <is>
-          <t xml:space="preserve">5:39</t>
+          <t xml:space="preserve">6:1</t>
         </is>
       </c>
       <c s="13" t="str" r="AF56"/>
@@ -26590,9 +28410,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ57"/>
-      <c s="15" t="str" r="AK57"/>
-      <c s="15" t="str" r="AL57"/>
+      <c s="15" t="inlineStr" r="AJ57">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK57">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL57">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM57"/>
     </row>
     <row r="58" ht="15.35" customHeight="0">
@@ -26745,9 +28577,21 @@
           <t xml:space="preserve">12:27</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ58"/>
-      <c s="18" t="str" r="AK58"/>
-      <c s="20" t="str" r="AL58"/>
+      <c s="18" t="inlineStr" r="AJ58">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK58">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL58">
+        <is>
+          <t xml:space="preserve">12:07</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM58"/>
     </row>
     <row r="59" ht="15.3" customHeight="0">
@@ -26900,9 +28744,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ59"/>
-      <c s="20" t="str" r="AK59"/>
-      <c s="20" t="str" r="AL59"/>
+      <c s="20" t="inlineStr" r="AJ59">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK59">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL59">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM59"/>
     </row>
     <row r="60" ht="15.3" customHeight="0">
@@ -27055,9 +28911,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ60"/>
-      <c s="20" t="str" r="AK60"/>
-      <c s="20" t="str" r="AL60"/>
+      <c s="20" t="inlineStr" r="AJ60">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK60">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL60">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM60"/>
     </row>
     <row r="61" ht="15.35" customHeight="0">
@@ -27210,9 +29078,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ61"/>
-      <c s="20" t="str" r="AK61"/>
-      <c s="20" t="str" r="AL61"/>
+      <c s="20" t="inlineStr" r="AJ61">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK61">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL61">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM61"/>
     </row>
     <row r="62" ht="14.6" customHeight="0">
@@ -27365,9 +29245,21 @@
           <t xml:space="preserve">P-LT</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ62"/>
-      <c s="20" t="str" r="AK62"/>
-      <c s="20" t="str" r="AL62"/>
+      <c s="20" t="inlineStr" r="AJ62">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK62">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL62">
+        <is>
+          <t xml:space="preserve">P/2</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM62"/>
     </row>
     <row r="63" ht="14.6" customHeight="0">
@@ -27520,9 +29412,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ63"/>
-      <c s="24" t="str" r="AK63"/>
-      <c s="24" t="str" r="AL63"/>
+      <c s="24" t="inlineStr" r="AJ63">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK63">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL63">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM63"/>
     </row>
     <row r="64" ht="15.3" customHeight="0">
@@ -27948,7 +29852,7 @@
     <row r="1" ht="17" customHeight="0">
       <c s="1" t="inlineStr" r="B1">
         <is>
-          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 28-10-2026</t>
+          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 31-10-2026</t>
         </is>
       </c>
       <c s="2" t="inlineStr" r="P1">
@@ -27958,7 +29862,7 @@
       </c>
       <c s="3" t="inlineStr" r="AF1">
         <is>
-          <t xml:space="preserve">Print Date 28-10-2026</t>
+          <t xml:space="preserve">Print Date 31-10-2026</t>
         </is>
       </c>
     </row>
@@ -28175,7 +30079,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -28370,9 +30274,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ7"/>
-      <c s="15" t="str" r="AK7"/>
-      <c s="15" t="str" r="AL7"/>
+      <c s="15" t="inlineStr" r="AJ7">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK7">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL7">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM7"/>
     </row>
     <row r="8" ht="15.3" customHeight="0">
@@ -28525,9 +30441,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ8"/>
-      <c s="18" t="str" r="AK8"/>
-      <c s="20" t="str" r="AL8"/>
+      <c s="18" t="inlineStr" r="AJ8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM8"/>
     </row>
     <row r="9" ht="15.3" customHeight="0">
@@ -28680,9 +30608,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ9"/>
-      <c s="20" t="str" r="AK9"/>
-      <c s="20" t="str" r="AL9"/>
+      <c s="20" t="inlineStr" r="AJ9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM9"/>
     </row>
     <row r="10" ht="15.35" customHeight="0">
@@ -28835,9 +30775,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ10"/>
-      <c s="20" t="str" r="AK10"/>
-      <c s="20" t="str" r="AL10"/>
+      <c s="20" t="inlineStr" r="AJ10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM10"/>
     </row>
     <row r="11" ht="15.3" customHeight="0">
@@ -28990,9 +30942,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ11"/>
-      <c s="20" t="str" r="AK11"/>
-      <c s="20" t="str" r="AL11"/>
+      <c s="20" t="inlineStr" r="AJ11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM11"/>
     </row>
     <row r="12" ht="14.6" customHeight="0">
@@ -29145,9 +31109,21 @@
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ12"/>
-      <c s="20" t="str" r="AK12"/>
-      <c s="20" t="str" r="AL12"/>
+      <c s="20" t="inlineStr" r="AJ12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM12"/>
     </row>
     <row r="13" ht="14.6" customHeight="0">
@@ -29300,9 +31276,21 @@
           <t xml:space="preserve">001</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ13"/>
-      <c s="24" t="str" r="AK13"/>
-      <c s="24" t="str" r="AL13"/>
+      <c s="24" t="inlineStr" r="AJ13">
+        <is>
+          <t xml:space="preserve">001</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK13">
+        <is>
+          <t xml:space="preserve">001</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL13">
+        <is>
+          <t xml:space="preserve">001</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM13"/>
     </row>
     <row r="14" ht="15.3" customHeight="0">
@@ -29434,7 +31422,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">17.5</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -29453,7 +31441,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">5.5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -29471,7 +31459,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">22.5</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -29482,7 +31470,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE16">
         <is>
-          <t xml:space="preserve">32:1</t>
+          <t xml:space="preserve">32:44</t>
         </is>
       </c>
       <c s="13" t="str" r="AF16"/>
@@ -29648,9 +31636,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ17"/>
-      <c s="15" t="str" r="AK17"/>
-      <c s="15" t="str" r="AL17"/>
+      <c s="15" t="inlineStr" r="AJ17">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK17">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL17">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM17"/>
     </row>
     <row r="18" ht="15.35" customHeight="0">
@@ -29803,9 +31803,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ18"/>
-      <c s="18" t="str" r="AK18"/>
-      <c s="20" t="str" r="AL18"/>
+      <c s="18" t="inlineStr" r="AJ18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL18">
+        <is>
+          <t xml:space="preserve">11:43</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM18"/>
     </row>
     <row r="19" ht="15.3" customHeight="0">
@@ -29958,9 +31970,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ19"/>
-      <c s="20" t="str" r="AK19"/>
-      <c s="20" t="str" r="AL19"/>
+      <c s="20" t="inlineStr" r="AJ19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM19"/>
     </row>
     <row r="20" ht="15.35" customHeight="0">
@@ -30113,9 +32137,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ20"/>
-      <c s="20" t="str" r="AK20"/>
-      <c s="20" t="str" r="AL20"/>
+      <c s="20" t="inlineStr" r="AJ20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM20"/>
     </row>
     <row r="21" ht="15.3" customHeight="0">
@@ -30268,9 +32304,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ21"/>
-      <c s="20" t="str" r="AK21"/>
-      <c s="20" t="str" r="AL21"/>
+      <c s="20" t="inlineStr" r="AJ21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM21"/>
     </row>
     <row r="22" ht="14.6" customHeight="0">
@@ -30423,9 +32471,21 @@
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ22"/>
-      <c s="20" t="str" r="AK22"/>
-      <c s="20" t="str" r="AL22"/>
+      <c s="20" t="inlineStr" r="AJ22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL22">
+        <is>
+          <t xml:space="preserve">P/2</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM22"/>
     </row>
     <row r="23" ht="14.6" customHeight="0">
@@ -30578,9 +32638,21 @@
           <t xml:space="preserve">001</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ23"/>
-      <c s="24" t="str" r="AK23"/>
-      <c s="24" t="str" r="AL23"/>
+      <c s="24" t="inlineStr" r="AJ23">
+        <is>
+          <t xml:space="preserve">001</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK23">
+        <is>
+          <t xml:space="preserve">001</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL23">
+        <is>
+          <t xml:space="preserve">001</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM23"/>
     </row>
     <row r="24" ht="15.3" customHeight="0">
@@ -30774,7 +32846,7 @@
     <row r="1" ht="17" customHeight="0">
       <c s="1" t="inlineStr" r="B1">
         <is>
-          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 28-10-2026</t>
+          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 31-10-2026</t>
         </is>
       </c>
       <c s="2" t="inlineStr" r="P1">
@@ -30784,7 +32856,7 @@
       </c>
       <c s="3" t="inlineStr" r="AF1">
         <is>
-          <t xml:space="preserve">Print Date 28-10-2026</t>
+          <t xml:space="preserve">Print Date 31-10-2026</t>
         </is>
       </c>
     </row>
@@ -30982,7 +33054,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -31001,7 +33073,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -31019,7 +33091,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -31204,9 +33276,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ7"/>
-      <c s="15" t="str" r="AK7"/>
-      <c s="15" t="str" r="AL7"/>
+      <c s="15" t="inlineStr" r="AJ7">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK7">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL7">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM7"/>
     </row>
     <row r="8" ht="15.3" customHeight="0">
@@ -31359,9 +33443,21 @@
           <t xml:space="preserve">11:25</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ8"/>
-      <c s="18" t="str" r="AK8"/>
-      <c s="20" t="str" r="AL8"/>
+      <c s="18" t="inlineStr" r="AJ8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL8">
+        <is>
+          <t xml:space="preserve">11:26</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM8"/>
     </row>
     <row r="9" ht="15.3" customHeight="0">
@@ -31514,9 +33610,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ9"/>
-      <c s="20" t="str" r="AK9"/>
-      <c s="20" t="str" r="AL9"/>
+      <c s="20" t="inlineStr" r="AJ9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM9"/>
     </row>
     <row r="10" ht="15.35" customHeight="0">
@@ -31669,9 +33777,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ10"/>
-      <c s="20" t="str" r="AK10"/>
-      <c s="20" t="str" r="AL10"/>
+      <c s="20" t="inlineStr" r="AJ10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM10"/>
     </row>
     <row r="11" ht="15.3" customHeight="0">
@@ -31824,9 +33944,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ11"/>
-      <c s="20" t="str" r="AK11"/>
-      <c s="20" t="str" r="AL11"/>
+      <c s="20" t="inlineStr" r="AJ11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM11"/>
     </row>
     <row r="12" ht="14.6" customHeight="0">
@@ -31979,9 +34111,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ12"/>
-      <c s="20" t="str" r="AK12"/>
-      <c s="20" t="str" r="AL12"/>
+      <c s="20" t="inlineStr" r="AJ12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL12">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM12"/>
     </row>
     <row r="13" ht="14.6" customHeight="0">
@@ -32134,9 +34278,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ13"/>
-      <c s="24" t="str" r="AK13"/>
-      <c s="24" t="str" r="AL13"/>
+      <c s="24" t="inlineStr" r="AJ13">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK13">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL13">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM13"/>
     </row>
     <row r="14" ht="15.3" customHeight="0">
@@ -32268,7 +34424,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -32287,7 +34443,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -32305,7 +34461,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -32482,9 +34638,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ17"/>
-      <c s="15" t="str" r="AK17"/>
-      <c s="15" t="str" r="AL17"/>
+      <c s="15" t="inlineStr" r="AJ17">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK17">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL17">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM17"/>
     </row>
     <row r="18" ht="15.35" customHeight="0">
@@ -32637,9 +34805,21 @@
           <t xml:space="preserve">11:57</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ18"/>
-      <c s="18" t="str" r="AK18"/>
-      <c s="20" t="str" r="AL18"/>
+      <c s="18" t="inlineStr" r="AJ18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL18">
+        <is>
+          <t xml:space="preserve">11:55</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM18"/>
     </row>
     <row r="19" ht="15.3" customHeight="0">
@@ -32792,9 +34972,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ19"/>
-      <c s="20" t="str" r="AK19"/>
-      <c s="20" t="str" r="AL19"/>
+      <c s="20" t="inlineStr" r="AJ19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM19"/>
     </row>
     <row r="20" ht="15.35" customHeight="0">
@@ -32947,9 +35139,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ20"/>
-      <c s="20" t="str" r="AK20"/>
-      <c s="20" t="str" r="AL20"/>
+      <c s="20" t="inlineStr" r="AJ20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM20"/>
     </row>
     <row r="21" ht="15.3" customHeight="0">
@@ -33102,9 +35306,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ21"/>
-      <c s="20" t="str" r="AK21"/>
-      <c s="20" t="str" r="AL21"/>
+      <c s="20" t="inlineStr" r="AJ21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM21"/>
     </row>
     <row r="22" ht="14.6" customHeight="0">
@@ -33257,9 +35473,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ22"/>
-      <c s="20" t="str" r="AK22"/>
-      <c s="20" t="str" r="AL22"/>
+      <c s="20" t="inlineStr" r="AJ22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL22">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM22"/>
     </row>
     <row r="23" ht="14.6" customHeight="0">
@@ -33412,9 +35640,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ23"/>
-      <c s="24" t="str" r="AK23"/>
-      <c s="24" t="str" r="AL23"/>
+      <c s="24" t="inlineStr" r="AJ23">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK23">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL23">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM23"/>
     </row>
     <row r="24" ht="15.3" customHeight="0">
@@ -33546,7 +35786,7 @@
       <c s="13" t="str" r="N26"/>
       <c s="12" t="inlineStr" r="O26">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c s="13" t="str" r="P26"/>
@@ -33565,7 +35805,7 @@
       <c s="13" t="str" r="U26"/>
       <c s="12" t="inlineStr" r="V26">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c s="13" t="str" r="W26"/>
@@ -33583,7 +35823,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB26">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c s="13" t="str" r="AC26"/>
@@ -33594,7 +35834,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE26">
         <is>
-          <t xml:space="preserve">7:4</t>
+          <t xml:space="preserve">7:25</t>
         </is>
       </c>
       <c s="13" t="str" r="AF26"/>
@@ -33768,9 +36008,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ27"/>
-      <c s="15" t="str" r="AK27"/>
-      <c s="15" t="str" r="AL27"/>
+      <c s="15" t="inlineStr" r="AJ27">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK27">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL27">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM27"/>
     </row>
     <row r="28" ht="15.35" customHeight="0">
@@ -33923,9 +36175,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ28"/>
-      <c s="18" t="str" r="AK28"/>
-      <c s="20" t="str" r="AL28"/>
+      <c s="18" t="inlineStr" r="AJ28">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK28">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL28">
+        <is>
+          <t xml:space="preserve">11:51</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM28"/>
     </row>
     <row r="29" ht="15.3" customHeight="0">
@@ -34078,9 +36342,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ29"/>
-      <c s="20" t="str" r="AK29"/>
-      <c s="20" t="str" r="AL29"/>
+      <c s="20" t="inlineStr" r="AJ29">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK29">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL29">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM29"/>
     </row>
     <row r="30" ht="15.35" customHeight="0">
@@ -34233,9 +36509,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ30"/>
-      <c s="20" t="str" r="AK30"/>
-      <c s="20" t="str" r="AL30"/>
+      <c s="20" t="inlineStr" r="AJ30">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK30">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL30">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM30"/>
     </row>
     <row r="31" ht="15.3" customHeight="0">
@@ -34388,9 +36676,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ31"/>
-      <c s="20" t="str" r="AK31"/>
-      <c s="20" t="str" r="AL31"/>
+      <c s="20" t="inlineStr" r="AJ31">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK31">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL31">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM31"/>
     </row>
     <row r="32" ht="14.6" customHeight="0">
@@ -34543,9 +36843,21 @@
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ32"/>
-      <c s="20" t="str" r="AK32"/>
-      <c s="20" t="str" r="AL32"/>
+      <c s="20" t="inlineStr" r="AJ32">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK32">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL32">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM32"/>
     </row>
     <row r="33" ht="14.6" customHeight="0">
@@ -34698,9 +37010,21 @@
           <t xml:space="preserve">003</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ33"/>
-      <c s="24" t="str" r="AK33"/>
-      <c s="24" t="str" r="AL33"/>
+      <c s="24" t="inlineStr" r="AJ33">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK33">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL33">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM33"/>
     </row>
     <row r="34" ht="15.3" customHeight="0">
@@ -34832,7 +37156,7 @@
       <c s="13" t="str" r="N36"/>
       <c s="12" t="inlineStr" r="O36">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c s="13" t="str" r="P36"/>
@@ -34851,7 +37175,7 @@
       <c s="13" t="str" r="U36"/>
       <c s="12" t="inlineStr" r="V36">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c s="13" t="str" r="W36"/>
@@ -34869,7 +37193,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB36">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c s="13" t="str" r="AC36"/>
@@ -35054,9 +37378,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ37"/>
-      <c s="15" t="str" r="AK37"/>
-      <c s="15" t="str" r="AL37"/>
+      <c s="15" t="inlineStr" r="AJ37">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK37">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL37">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM37"/>
     </row>
     <row r="38" ht="15.35" customHeight="0">
@@ -35209,9 +37545,21 @@
           <t xml:space="preserve">11:25</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ38"/>
-      <c s="18" t="str" r="AK38"/>
-      <c s="20" t="str" r="AL38"/>
+      <c s="18" t="inlineStr" r="AJ38">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK38">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL38">
+        <is>
+          <t xml:space="preserve">11:21</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM38"/>
     </row>
     <row r="39" ht="15.3" customHeight="0">
@@ -35364,9 +37712,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ39"/>
-      <c s="20" t="str" r="AK39"/>
-      <c s="20" t="str" r="AL39"/>
+      <c s="20" t="inlineStr" r="AJ39">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK39">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL39">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM39"/>
     </row>
     <row r="40" ht="15.3" customHeight="0">
@@ -35519,9 +37879,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ40"/>
-      <c s="20" t="str" r="AK40"/>
-      <c s="20" t="str" r="AL40"/>
+      <c s="20" t="inlineStr" r="AJ40">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK40">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL40">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM40"/>
     </row>
     <row r="41" ht="15.35" customHeight="0">
@@ -35674,9 +38046,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ41"/>
-      <c s="20" t="str" r="AK41"/>
-      <c s="20" t="str" r="AL41"/>
+      <c s="20" t="inlineStr" r="AJ41">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK41">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL41">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM41"/>
     </row>
     <row r="42" ht="14.6" customHeight="0">
@@ -35829,9 +38213,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ42"/>
-      <c s="20" t="str" r="AK42"/>
-      <c s="20" t="str" r="AL42"/>
+      <c s="20" t="inlineStr" r="AJ42">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK42">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL42">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM42"/>
     </row>
     <row r="43" ht="14.6" customHeight="0">
@@ -35984,9 +38380,21 @@
           <t xml:space="preserve">003</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ43"/>
-      <c s="24" t="str" r="AK43"/>
-      <c s="24" t="str" r="AL43"/>
+      <c s="24" t="inlineStr" r="AJ43">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK43">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL43">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM43"/>
     </row>
     <row r="44" ht="15.3" customHeight="0">
@@ -36118,7 +38526,7 @@
       <c s="13" t="str" r="N46"/>
       <c s="12" t="inlineStr" r="O46">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c s="13" t="str" r="P46"/>
@@ -36137,7 +38545,7 @@
       <c s="13" t="str" r="U46"/>
       <c s="12" t="inlineStr" r="V46">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c s="13" t="str" r="W46"/>
@@ -36155,7 +38563,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB46">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c s="13" t="str" r="AC46"/>
@@ -36178,13 +38586,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI46">
         <is>
-          <t xml:space="preserve">171:8</t>
+          <t xml:space="preserve">161:58</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ46"/>
       <c s="12" t="inlineStr" r="AK46">
         <is>
-          <t xml:space="preserve">20:12</t>
+          <t xml:space="preserve">11:2</t>
         </is>
       </c>
       <c s="13" t="str" r="AL46"/>
@@ -36340,9 +38748,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ47"/>
-      <c s="15" t="str" r="AK47"/>
-      <c s="15" t="str" r="AL47"/>
+      <c s="15" t="inlineStr" r="AJ47">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK47">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL47">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM47"/>
     </row>
     <row r="48" ht="15.35" customHeight="0">
@@ -36358,7 +38778,7 @@
       </c>
       <c s="18" t="inlineStr" r="E48">
         <is>
-          <t xml:space="preserve">11:40</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="F48">
@@ -36495,9 +38915,21 @@
           <t xml:space="preserve">11:45</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ48"/>
-      <c s="18" t="str" r="AK48"/>
-      <c s="20" t="str" r="AL48"/>
+      <c s="18" t="inlineStr" r="AJ48">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK48">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL48">
+        <is>
+          <t xml:space="preserve">11:45</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM48"/>
     </row>
     <row r="49" ht="15.3" customHeight="0">
@@ -36513,7 +38945,7 @@
       </c>
       <c s="20" t="inlineStr" r="E49">
         <is>
-          <t xml:space="preserve">20:50</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F49">
@@ -36650,9 +39082,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ49"/>
-      <c s="20" t="str" r="AK49"/>
-      <c s="20" t="str" r="AL49"/>
+      <c s="20" t="inlineStr" r="AJ49">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK49">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL49">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM49"/>
     </row>
     <row r="50" ht="15.3" customHeight="0">
@@ -36668,7 +39112,7 @@
       </c>
       <c s="20" t="inlineStr" r="E50">
         <is>
-          <t xml:space="preserve">09:10</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F50">
@@ -36805,9 +39249,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ50"/>
-      <c s="20" t="str" r="AK50"/>
-      <c s="20" t="str" r="AL50"/>
+      <c s="20" t="inlineStr" r="AJ50">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK50">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL50">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM50"/>
     </row>
     <row r="51" ht="15.35" customHeight="0">
@@ -36823,7 +39279,7 @@
       </c>
       <c s="20" t="inlineStr" r="E51">
         <is>
-          <t xml:space="preserve">09:10</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F51">
@@ -36960,9 +39416,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ51"/>
-      <c s="20" t="str" r="AK51"/>
-      <c s="20" t="str" r="AL51"/>
+      <c s="20" t="inlineStr" r="AJ51">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK51">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL51">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM51"/>
     </row>
     <row r="52" ht="14.6" customHeight="0">
@@ -36978,7 +39446,7 @@
       </c>
       <c s="20" t="inlineStr" r="E52">
         <is>
-          <t xml:space="preserve">POH</t>
+          <t xml:space="preserve">HLD</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F52">
@@ -37115,9 +39583,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ52"/>
-      <c s="20" t="str" r="AK52"/>
-      <c s="20" t="str" r="AL52"/>
+      <c s="20" t="inlineStr" r="AJ52">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK52">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL52">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM52"/>
     </row>
     <row r="53" ht="14.6" customHeight="0">
@@ -37270,9 +39750,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ53"/>
-      <c s="24" t="str" r="AK53"/>
-      <c s="24" t="str" r="AL53"/>
+      <c s="24" t="inlineStr" r="AJ53">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK53">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL53">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM53"/>
     </row>
     <row r="54" ht="15.3" customHeight="0">
@@ -37404,7 +39896,7 @@
       <c s="13" t="str" r="N56"/>
       <c s="12" t="inlineStr" r="O56">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c s="13" t="str" r="P56"/>
@@ -37423,7 +39915,7 @@
       <c s="13" t="str" r="U56"/>
       <c s="12" t="inlineStr" r="V56">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c s="13" t="str" r="W56"/>
@@ -37441,7 +39933,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB56">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c s="13" t="str" r="AC56"/>
@@ -37622,9 +40114,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ57"/>
-      <c s="15" t="str" r="AK57"/>
-      <c s="15" t="str" r="AL57"/>
+      <c s="15" t="inlineStr" r="AJ57">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK57">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL57">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM57"/>
     </row>
     <row r="58" ht="15.35" customHeight="0">
@@ -37777,9 +40281,21 @@
           <t xml:space="preserve">11:38</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ58"/>
-      <c s="18" t="str" r="AK58"/>
-      <c s="20" t="str" r="AL58"/>
+      <c s="18" t="inlineStr" r="AJ58">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK58">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL58">
+        <is>
+          <t xml:space="preserve">11:43</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM58"/>
     </row>
     <row r="59" ht="15.3" customHeight="0">
@@ -37932,9 +40448,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ59"/>
-      <c s="20" t="str" r="AK59"/>
-      <c s="20" t="str" r="AL59"/>
+      <c s="20" t="inlineStr" r="AJ59">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK59">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL59">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM59"/>
     </row>
     <row r="60" ht="15.3" customHeight="0">
@@ -38087,9 +40615,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ60"/>
-      <c s="20" t="str" r="AK60"/>
-      <c s="20" t="str" r="AL60"/>
+      <c s="20" t="inlineStr" r="AJ60">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK60">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL60">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM60"/>
     </row>
     <row r="61" ht="15.35" customHeight="0">
@@ -38242,9 +40782,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ61"/>
-      <c s="20" t="str" r="AK61"/>
-      <c s="20" t="str" r="AL61"/>
+      <c s="20" t="inlineStr" r="AJ61">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK61">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL61">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM61"/>
     </row>
     <row r="62" ht="14.6" customHeight="0">
@@ -38397,9 +40949,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ62"/>
-      <c s="20" t="str" r="AK62"/>
-      <c s="20" t="str" r="AL62"/>
+      <c s="20" t="inlineStr" r="AJ62">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK62">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL62">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM62"/>
     </row>
     <row r="63" ht="14.6" customHeight="0">
@@ -38552,9 +41116,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ63"/>
-      <c s="24" t="str" r="AK63"/>
-      <c s="24" t="str" r="AL63"/>
+      <c s="24" t="inlineStr" r="AJ63">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK63">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL63">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM63"/>
     </row>
     <row r="64" ht="15.3" customHeight="0">
@@ -38686,7 +41262,7 @@
       <c s="13" t="str" r="N66"/>
       <c s="12" t="inlineStr" r="O66">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c s="13" t="str" r="P66"/>
@@ -38705,7 +41281,7 @@
       <c s="13" t="str" r="U66"/>
       <c s="12" t="inlineStr" r="V66">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c s="13" t="str" r="W66"/>
@@ -38723,7 +41299,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB66">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c s="13" t="str" r="AC66"/>
@@ -38904,9 +41480,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ67"/>
-      <c s="15" t="str" r="AK67"/>
-      <c s="15" t="str" r="AL67"/>
+      <c s="15" t="inlineStr" r="AJ67">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK67">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL67">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM67"/>
     </row>
     <row r="68" ht="15.35" customHeight="0">
@@ -39059,9 +41647,21 @@
           <t xml:space="preserve">11:58</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ68"/>
-      <c s="18" t="str" r="AK68"/>
-      <c s="20" t="str" r="AL68"/>
+      <c s="18" t="inlineStr" r="AJ68">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK68">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL68">
+        <is>
+          <t xml:space="preserve">12:02</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM68"/>
     </row>
     <row r="69" ht="15.3" customHeight="0">
@@ -39214,9 +41814,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ69"/>
-      <c s="20" t="str" r="AK69"/>
-      <c s="20" t="str" r="AL69"/>
+      <c s="20" t="inlineStr" r="AJ69">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK69">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL69">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM69"/>
     </row>
     <row r="70" ht="15.3" customHeight="0">
@@ -39369,9 +41981,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ70"/>
-      <c s="20" t="str" r="AK70"/>
-      <c s="20" t="str" r="AL70"/>
+      <c s="20" t="inlineStr" r="AJ70">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK70">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL70">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM70"/>
     </row>
     <row r="71" ht="15.35" customHeight="0">
@@ -39524,9 +42148,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ71"/>
-      <c s="20" t="str" r="AK71"/>
-      <c s="20" t="str" r="AL71"/>
+      <c s="20" t="inlineStr" r="AJ71">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK71">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL71">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM71"/>
     </row>
     <row r="72" ht="14.6" customHeight="0">
@@ -39679,9 +42315,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ72"/>
-      <c s="20" t="str" r="AK72"/>
-      <c s="20" t="str" r="AL72"/>
+      <c s="20" t="inlineStr" r="AJ72">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK72">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL72">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM72"/>
     </row>
     <row r="73" ht="14.6" customHeight="0">
@@ -39834,9 +42482,21 @@
           <t xml:space="preserve">005</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ73"/>
-      <c s="24" t="str" r="AK73"/>
-      <c s="24" t="str" r="AL73"/>
+      <c s="24" t="inlineStr" r="AJ73">
+        <is>
+          <t xml:space="preserve">005</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK73">
+        <is>
+          <t xml:space="preserve">005</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL73">
+        <is>
+          <t xml:space="preserve">005</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM73"/>
     </row>
     <row r="74" ht="15.3" customHeight="0">
@@ -39968,7 +42628,7 @@
       <c s="13" t="str" r="N76"/>
       <c s="12" t="inlineStr" r="O76">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c s="13" t="str" r="P76"/>
@@ -39987,7 +42647,7 @@
       <c s="13" t="str" r="U76"/>
       <c s="12" t="inlineStr" r="V76">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c s="13" t="str" r="W76"/>
@@ -40005,7 +42665,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB76">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c s="13" t="str" r="AC76"/>
@@ -40016,7 +42676,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE76">
         <is>
-          <t xml:space="preserve">00:34</t>
+          <t xml:space="preserve">1:18</t>
         </is>
       </c>
       <c s="13" t="str" r="AF76"/>
@@ -40190,9 +42850,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ77"/>
-      <c s="15" t="str" r="AK77"/>
-      <c s="15" t="str" r="AL77"/>
+      <c s="15" t="inlineStr" r="AJ77">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK77">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL77">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM77"/>
     </row>
     <row r="78" ht="15.3" customHeight="0">
@@ -40345,9 +43017,21 @@
           <t xml:space="preserve">11:25</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ78"/>
-      <c s="18" t="str" r="AK78"/>
-      <c s="20" t="str" r="AL78"/>
+      <c s="18" t="inlineStr" r="AJ78">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK78">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL78">
+        <is>
+          <t xml:space="preserve">12:14</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM78"/>
     </row>
     <row r="79" ht="15.35" customHeight="0">
@@ -40500,9 +43184,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ79"/>
-      <c s="20" t="str" r="AK79"/>
-      <c s="20" t="str" r="AL79"/>
+      <c s="20" t="inlineStr" r="AJ79">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK79">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL79">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM79"/>
     </row>
     <row r="80" ht="15.3" customHeight="0">
@@ -40655,9 +43351,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ80"/>
-      <c s="20" t="str" r="AK80"/>
-      <c s="20" t="str" r="AL80"/>
+      <c s="20" t="inlineStr" r="AJ80">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK80">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL80">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM80"/>
     </row>
     <row r="81" ht="15.35" customHeight="0">
@@ -40810,9 +43518,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ81"/>
-      <c s="20" t="str" r="AK81"/>
-      <c s="20" t="str" r="AL81"/>
+      <c s="20" t="inlineStr" r="AJ81">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK81">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL81">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM81"/>
     </row>
     <row r="82" ht="14.6" customHeight="0">
@@ -40965,9 +43685,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ82"/>
-      <c s="20" t="str" r="AK82"/>
-      <c s="20" t="str" r="AL82"/>
+      <c s="20" t="inlineStr" r="AJ82">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK82">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL82">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM82"/>
     </row>
     <row r="83" ht="14.6" customHeight="0">
@@ -41120,9 +43852,21 @@
           <t xml:space="preserve">003</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ83"/>
-      <c s="24" t="str" r="AK83"/>
-      <c s="24" t="str" r="AL83"/>
+      <c s="24" t="inlineStr" r="AJ83">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK83">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL83">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM83"/>
     </row>
     <row r="84" ht="15.3" customHeight="0">
@@ -41273,7 +44017,7 @@
       <c s="13" t="str" r="U86"/>
       <c s="12" t="inlineStr" r="V86">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c s="13" t="str" r="W86"/>
@@ -41391,9 +44135,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="S87"/>
-      <c s="15" t="str" r="T87"/>
-      <c s="15" t="str" r="U87"/>
+      <c s="15" t="inlineStr" r="S87">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="T87">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="U87">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="15" t="str" r="V87"/>
       <c s="15" t="str" r="W87"/>
       <c s="15" t="str" r="X87"/>
@@ -41563,9 +44319,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ88"/>
-      <c s="18" t="str" r="AK88"/>
-      <c s="20" t="str" r="AL88"/>
+      <c s="18" t="inlineStr" r="AJ88">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK88">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL88">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM88"/>
     </row>
     <row r="89" ht="15.35" customHeight="0">
@@ -41718,9 +44486,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ89"/>
-      <c s="20" t="str" r="AK89"/>
-      <c s="20" t="str" r="AL89"/>
+      <c s="20" t="inlineStr" r="AJ89">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK89">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL89">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM89"/>
     </row>
     <row r="90" ht="15.3" customHeight="0">
@@ -41873,9 +44653,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ90"/>
-      <c s="20" t="str" r="AK90"/>
-      <c s="20" t="str" r="AL90"/>
+      <c s="20" t="inlineStr" r="AJ90">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK90">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL90">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM90"/>
     </row>
     <row r="91" ht="15.35" customHeight="0">
@@ -42028,9 +44820,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ91"/>
-      <c s="20" t="str" r="AK91"/>
-      <c s="20" t="str" r="AL91"/>
+      <c s="20" t="inlineStr" r="AJ91">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK91">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL91">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM91"/>
     </row>
     <row r="92" ht="14.55" customHeight="0">
@@ -42108,17 +44912,17 @@
       </c>
       <c s="20" t="inlineStr" r="S92">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="T92">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="U92">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="V92">
@@ -42183,9 +44987,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ92"/>
-      <c s="20" t="str" r="AK92"/>
-      <c s="20" t="str" r="AL92"/>
+      <c s="20" t="inlineStr" r="AJ92">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK92">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL92">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM92"/>
     </row>
     <row r="93" ht="14.6" customHeight="0">
@@ -42261,9 +45077,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="S93"/>
-      <c s="24" t="str" r="T93"/>
-      <c s="24" t="str" r="U93"/>
+      <c s="24" t="inlineStr" r="S93">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="T93">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="U93">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="24" t="str" r="V93"/>
       <c s="24" t="str" r="W93"/>
       <c s="24" t="str" r="X93"/>
@@ -42431,7 +45259,7 @@
       <c s="13" t="str" r="U96"/>
       <c s="12" t="inlineStr" r="V96">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c s="13" t="str" r="W96"/>
@@ -42468,13 +45296,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI96">
         <is>
-          <t xml:space="preserve">129:40</t>
+          <t xml:space="preserve">120:21</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ96"/>
       <c s="12" t="inlineStr" r="AK96">
         <is>
-          <t xml:space="preserve">21:52</t>
+          <t xml:space="preserve">12:33</t>
         </is>
       </c>
       <c s="13" t="str" r="AL96"/>
@@ -42630,9 +45458,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ97"/>
-      <c s="15" t="str" r="AK97"/>
-      <c s="15" t="str" r="AL97"/>
+      <c s="15" t="inlineStr" r="AJ97">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK97">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL97">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM97"/>
     </row>
     <row r="98" ht="15.3" customHeight="0">
@@ -42648,7 +45488,7 @@
       </c>
       <c s="18" t="inlineStr" r="E98">
         <is>
-          <t xml:space="preserve">11:16</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="F98">
@@ -42785,9 +45625,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ98"/>
-      <c s="18" t="str" r="AK98"/>
-      <c s="20" t="str" r="AL98"/>
+      <c s="18" t="inlineStr" r="AJ98">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK98">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL98">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM98"/>
     </row>
     <row r="99" ht="15.35" customHeight="0">
@@ -42803,7 +45655,7 @@
       </c>
       <c s="20" t="inlineStr" r="E99">
         <is>
-          <t xml:space="preserve">20:35</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F99">
@@ -42940,9 +45792,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ99"/>
-      <c s="20" t="str" r="AK99"/>
-      <c s="20" t="str" r="AL99"/>
+      <c s="20" t="inlineStr" r="AJ99">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK99">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL99">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM99"/>
     </row>
     <row r="100" ht="15.3" customHeight="0">
@@ -42958,7 +45822,7 @@
       </c>
       <c s="20" t="inlineStr" r="E100">
         <is>
-          <t xml:space="preserve">09:19</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F100">
@@ -43095,9 +45959,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ100"/>
-      <c s="20" t="str" r="AK100"/>
-      <c s="20" t="str" r="AL100"/>
+      <c s="20" t="inlineStr" r="AJ100">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK100">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL100">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM100"/>
     </row>
     <row r="101" ht="15.3" customHeight="0">
@@ -43113,7 +45989,7 @@
       </c>
       <c s="20" t="inlineStr" r="E101">
         <is>
-          <t xml:space="preserve">09:19</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F101">
@@ -43250,9 +46126,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ101"/>
-      <c s="20" t="str" r="AK101"/>
-      <c s="20" t="str" r="AL101"/>
+      <c s="20" t="inlineStr" r="AJ101">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK101">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL101">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM101"/>
     </row>
     <row r="102" ht="14.6" customHeight="0">
@@ -43268,7 +46156,7 @@
       </c>
       <c s="20" t="inlineStr" r="E102">
         <is>
-          <t xml:space="preserve">POH</t>
+          <t xml:space="preserve">HLD</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F102">
@@ -43405,9 +46293,21 @@
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ102"/>
-      <c s="20" t="str" r="AK102"/>
-      <c s="20" t="str" r="AL102"/>
+      <c s="20" t="inlineStr" r="AJ102">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK102">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL102">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM102"/>
     </row>
     <row r="103" ht="14.6" customHeight="0">
@@ -43560,9 +46460,21 @@
           <t xml:space="preserve">003</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ103"/>
-      <c s="24" t="str" r="AK103"/>
-      <c s="24" t="str" r="AL103"/>
+      <c s="24" t="inlineStr" r="AJ103">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK103">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL103">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM103"/>
     </row>
     <row r="104" ht="15.3" customHeight="0">
@@ -44221,7 +47133,7 @@
     <row r="1" ht="17" customHeight="0">
       <c s="1" t="inlineStr" r="B1">
         <is>
-          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 28-10-2026</t>
+          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 31-10-2026</t>
         </is>
       </c>
       <c s="2" t="inlineStr" r="P1">
@@ -44231,7 +47143,7 @@
       </c>
       <c s="3" t="inlineStr" r="AF1">
         <is>
-          <t xml:space="preserve">Print Date 28-10-2026</t>
+          <t xml:space="preserve">Print Date 31-10-2026</t>
         </is>
       </c>
     </row>
@@ -44429,7 +47341,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">18.5</t>
+          <t xml:space="preserve">19.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -44448,7 +47360,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">4.5</t>
+          <t xml:space="preserve">6.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -44466,7 +47378,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">23.5</t>
+          <t xml:space="preserve">24.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -44477,7 +47389,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE6">
         <is>
-          <t xml:space="preserve">2:35</t>
+          <t xml:space="preserve">3:1</t>
         </is>
       </c>
       <c s="13" t="str" r="AF6"/>
@@ -44647,9 +47559,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ7"/>
-      <c s="15" t="str" r="AK7"/>
-      <c s="15" t="str" r="AL7"/>
+      <c s="15" t="inlineStr" r="AJ7">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK7">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL7">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM7"/>
     </row>
     <row r="8" ht="15.3" customHeight="0">
@@ -44802,9 +47726,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ8"/>
-      <c s="18" t="str" r="AK8"/>
-      <c s="20" t="str" r="AL8"/>
+      <c s="18" t="inlineStr" r="AJ8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL8">
+        <is>
+          <t xml:space="preserve">12:26</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM8"/>
     </row>
     <row r="9" ht="15.3" customHeight="0">
@@ -44957,9 +47893,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ9"/>
-      <c s="20" t="str" r="AK9"/>
-      <c s="20" t="str" r="AL9"/>
+      <c s="20" t="inlineStr" r="AJ9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM9"/>
     </row>
     <row r="10" ht="15.35" customHeight="0">
@@ -45112,9 +48060,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ10"/>
-      <c s="20" t="str" r="AK10"/>
-      <c s="20" t="str" r="AL10"/>
+      <c s="20" t="inlineStr" r="AJ10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM10"/>
     </row>
     <row r="11" ht="15.3" customHeight="0">
@@ -45267,9 +48227,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ11"/>
-      <c s="20" t="str" r="AK11"/>
-      <c s="20" t="str" r="AL11"/>
+      <c s="20" t="inlineStr" r="AJ11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM11"/>
     </row>
     <row r="12" ht="14.6" customHeight="0">
@@ -45422,9 +48394,21 @@
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ12"/>
-      <c s="20" t="str" r="AK12"/>
-      <c s="20" t="str" r="AL12"/>
+      <c s="20" t="inlineStr" r="AJ12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL12">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM12"/>
     </row>
     <row r="13" ht="14.6" customHeight="0">
@@ -45577,9 +48561,21 @@
           <t xml:space="preserve">005</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ13"/>
-      <c s="24" t="str" r="AK13"/>
-      <c s="24" t="str" r="AL13"/>
+      <c s="24" t="inlineStr" r="AJ13">
+        <is>
+          <t xml:space="preserve">005</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK13">
+        <is>
+          <t xml:space="preserve">005</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL13">
+        <is>
+          <t xml:space="preserve">005</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM13"/>
     </row>
     <row r="14" ht="15.3" customHeight="0">
@@ -45711,7 +48707,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -45730,7 +48726,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -45748,7 +48744,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -45759,7 +48755,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE16">
         <is>
-          <t xml:space="preserve">1:20</t>
+          <t xml:space="preserve">1:50</t>
         </is>
       </c>
       <c s="13" t="str" r="AF16"/>
@@ -45771,13 +48767,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI16">
         <is>
-          <t xml:space="preserve">171:8</t>
+          <t xml:space="preserve">163:0</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ16"/>
       <c s="12" t="inlineStr" r="AK16">
         <is>
-          <t xml:space="preserve">16:16</t>
+          <t xml:space="preserve">8:8</t>
         </is>
       </c>
       <c s="13" t="str" r="AL16"/>
@@ -45933,9 +48929,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ17"/>
-      <c s="15" t="str" r="AK17"/>
-      <c s="15" t="str" r="AL17"/>
+      <c s="15" t="inlineStr" r="AJ17">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK17">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL17">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM17"/>
     </row>
     <row r="18" ht="15.35" customHeight="0">
@@ -45951,7 +48959,7 @@
       </c>
       <c s="18" t="inlineStr" r="E18">
         <is>
-          <t xml:space="preserve">11:57</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="F18">
@@ -46088,9 +49096,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ18"/>
-      <c s="18" t="str" r="AK18"/>
-      <c s="20" t="str" r="AL18"/>
+      <c s="18" t="inlineStr" r="AJ18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL18">
+        <is>
+          <t xml:space="preserve">12:15</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM18"/>
     </row>
     <row r="19" ht="15.3" customHeight="0">
@@ -46106,7 +49126,7 @@
       </c>
       <c s="20" t="inlineStr" r="E19">
         <is>
-          <t xml:space="preserve">20:05</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F19">
@@ -46243,9 +49263,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ19"/>
-      <c s="20" t="str" r="AK19"/>
-      <c s="20" t="str" r="AL19"/>
+      <c s="20" t="inlineStr" r="AJ19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM19"/>
     </row>
     <row r="20" ht="15.35" customHeight="0">
@@ -46261,7 +49293,7 @@
       </c>
       <c s="20" t="inlineStr" r="E20">
         <is>
-          <t xml:space="preserve">08:08</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F20">
@@ -46398,9 +49430,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ20"/>
-      <c s="20" t="str" r="AK20"/>
-      <c s="20" t="str" r="AL20"/>
+      <c s="20" t="inlineStr" r="AJ20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM20"/>
     </row>
     <row r="21" ht="15.3" customHeight="0">
@@ -46416,7 +49460,7 @@
       </c>
       <c s="20" t="inlineStr" r="E21">
         <is>
-          <t xml:space="preserve">08:08</t>
+          <t xml:space="preserve">00:00</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F21">
@@ -46553,9 +49597,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ21"/>
-      <c s="20" t="str" r="AK21"/>
-      <c s="20" t="str" r="AL21"/>
+      <c s="20" t="inlineStr" r="AJ21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM21"/>
     </row>
     <row r="22" ht="14.6" customHeight="0">
@@ -46571,7 +49627,7 @@
       </c>
       <c s="20" t="inlineStr" r="E22">
         <is>
-          <t xml:space="preserve">POH</t>
+          <t xml:space="preserve">HLD</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="F22">
@@ -46708,9 +49764,21 @@
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ22"/>
-      <c s="20" t="str" r="AK22"/>
-      <c s="20" t="str" r="AL22"/>
+      <c s="20" t="inlineStr" r="AJ22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL22">
+        <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM22"/>
     </row>
     <row r="23" ht="14.6" customHeight="0">
@@ -46863,9 +49931,21 @@
           <t xml:space="preserve">004</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ23"/>
-      <c s="24" t="str" r="AK23"/>
-      <c s="24" t="str" r="AL23"/>
+      <c s="24" t="inlineStr" r="AJ23">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK23">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL23">
+        <is>
+          <t xml:space="preserve">004</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM23"/>
     </row>
     <row r="24" ht="15.3" customHeight="0">
@@ -47059,7 +50139,7 @@
     <row r="1" ht="17" customHeight="0">
       <c s="1" t="inlineStr" r="B1">
         <is>
-          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 28-10-2026</t>
+          <t xml:space="preserve"> Report Date From : 01-10-2026 To : 31-10-2026</t>
         </is>
       </c>
       <c s="2" t="inlineStr" r="P1">
@@ -47069,7 +50149,7 @@
       </c>
       <c s="3" t="inlineStr" r="AF1">
         <is>
-          <t xml:space="preserve">Print Date 28-10-2026</t>
+          <t xml:space="preserve">Print Date 31-10-2026</t>
         </is>
       </c>
     </row>
@@ -47267,7 +50347,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -47286,7 +50366,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -47304,7 +50384,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -47489,9 +50569,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ7"/>
-      <c s="15" t="str" r="AK7"/>
-      <c s="15" t="str" r="AL7"/>
+      <c s="15" t="inlineStr" r="AJ7">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK7">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL7">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM7"/>
     </row>
     <row r="8" ht="15.3" customHeight="0">
@@ -47644,9 +50736,21 @@
           <t xml:space="preserve">11:24</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ8"/>
-      <c s="18" t="str" r="AK8"/>
-      <c s="20" t="str" r="AL8"/>
+      <c s="18" t="inlineStr" r="AJ8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK8">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL8">
+        <is>
+          <t xml:space="preserve">11:08</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM8"/>
     </row>
     <row r="9" ht="15.3" customHeight="0">
@@ -47799,9 +50903,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ9"/>
-      <c s="20" t="str" r="AK9"/>
-      <c s="20" t="str" r="AL9"/>
+      <c s="20" t="inlineStr" r="AJ9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL9">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM9"/>
     </row>
     <row r="10" ht="15.35" customHeight="0">
@@ -47954,9 +51070,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ10"/>
-      <c s="20" t="str" r="AK10"/>
-      <c s="20" t="str" r="AL10"/>
+      <c s="20" t="inlineStr" r="AJ10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL10">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM10"/>
     </row>
     <row r="11" ht="15.3" customHeight="0">
@@ -48109,9 +51237,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ11"/>
-      <c s="20" t="str" r="AK11"/>
-      <c s="20" t="str" r="AL11"/>
+      <c s="20" t="inlineStr" r="AJ11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL11">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM11"/>
     </row>
     <row r="12" ht="14.6" customHeight="0">
@@ -48264,9 +51404,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ12"/>
-      <c s="20" t="str" r="AK12"/>
-      <c s="20" t="str" r="AL12"/>
+      <c s="20" t="inlineStr" r="AJ12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK12">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL12">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM12"/>
     </row>
     <row r="13" ht="14.6" customHeight="0">
@@ -48419,9 +51571,21 @@
           <t xml:space="preserve">002</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ13"/>
-      <c s="24" t="str" r="AK13"/>
-      <c s="24" t="str" r="AL13"/>
+      <c s="24" t="inlineStr" r="AJ13">
+        <is>
+          <t xml:space="preserve">002</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK13">
+        <is>
+          <t xml:space="preserve">002</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL13">
+        <is>
+          <t xml:space="preserve">002</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM13"/>
     </row>
     <row r="14" ht="15.3" customHeight="0">
@@ -48553,7 +51717,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">20.5</t>
+          <t xml:space="preserve">21.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -48572,7 +51736,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">2.5</t>
+          <t xml:space="preserve">4.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -48590,7 +51754,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">25.5</t>
+          <t xml:space="preserve">26.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -48775,9 +51939,21 @@
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c s="15" t="str" r="AJ17"/>
-      <c s="15" t="str" r="AK17"/>
-      <c s="15" t="str" r="AL17"/>
+      <c s="15" t="inlineStr" r="AJ17">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AK17">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="AL17">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
       <c s="16" t="str" r="AM17"/>
     </row>
     <row r="18" ht="15.35" customHeight="0">
@@ -48930,9 +52106,21 @@
           <t xml:space="preserve">11:39</t>
         </is>
       </c>
-      <c s="18" t="str" r="AJ18"/>
-      <c s="18" t="str" r="AK18"/>
-      <c s="20" t="str" r="AL18"/>
+      <c s="18" t="inlineStr" r="AJ18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="AK18">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL18">
+        <is>
+          <t xml:space="preserve">11:45</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM18"/>
     </row>
     <row r="19" ht="15.3" customHeight="0">
@@ -49085,9 +52273,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ19"/>
-      <c s="20" t="str" r="AK19"/>
-      <c s="20" t="str" r="AL19"/>
+      <c s="20" t="inlineStr" r="AJ19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL19">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM19"/>
     </row>
     <row r="20" ht="15.35" customHeight="0">
@@ -49240,9 +52440,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ20"/>
-      <c s="20" t="str" r="AK20"/>
-      <c s="20" t="str" r="AL20"/>
+      <c s="20" t="inlineStr" r="AJ20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL20">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM20"/>
     </row>
     <row r="21" ht="15.3" customHeight="0">
@@ -49395,9 +52607,21 @@
           <t xml:space="preserve">00:00</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ21"/>
-      <c s="20" t="str" r="AK21"/>
-      <c s="20" t="str" r="AL21"/>
+      <c s="20" t="inlineStr" r="AJ21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL21">
+        <is>
+          <t xml:space="preserve">00:00</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM21"/>
     </row>
     <row r="22" ht="14.6" customHeight="0">
@@ -49550,9 +52774,21 @@
           <t xml:space="preserve">P</t>
         </is>
       </c>
-      <c s="20" t="str" r="AJ22"/>
-      <c s="20" t="str" r="AK22"/>
-      <c s="20" t="str" r="AL22"/>
+      <c s="20" t="inlineStr" r="AJ22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK22">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AL22">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
       <c s="21" t="str" r="AM22"/>
     </row>
     <row r="23" ht="14.6" customHeight="0">
@@ -49705,9 +52941,21 @@
           <t xml:space="preserve">003</t>
         </is>
       </c>
-      <c s="24" t="str" r="AJ23"/>
-      <c s="24" t="str" r="AK23"/>
-      <c s="24" t="str" r="AL23"/>
+      <c s="24" t="inlineStr" r="AJ23">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AK23">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
+      <c s="24" t="inlineStr" r="AL23">
+        <is>
+          <t xml:space="preserve">003</t>
+        </is>
+      </c>
       <c s="26" t="str" r="AM23"/>
     </row>
     <row r="24" ht="15.3" customHeight="0">

--- a/attendance_report.xlsx
+++ b/attendance_report.xlsx
@@ -692,7 +692,7 @@
       <c s="13" t="str" r="N7"/>
       <c s="12" t="inlineStr" r="O7">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c s="13" t="str" r="P7"/>
@@ -711,7 +711,7 @@
       <c s="13" t="str" r="U7"/>
       <c s="12" t="inlineStr" r="V7">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c s="13" t="str" r="W7"/>
@@ -729,7 +729,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB7">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c s="13" t="str" r="AC7"/>
@@ -740,7 +740,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE7">
         <is>
-          <t xml:space="preserve">42:18</t>
+          <t xml:space="preserve">45:40</t>
         </is>
       </c>
       <c s="13" t="str" r="AF7"/>
@@ -1079,7 +1079,7 @@
       </c>
       <c s="18" t="inlineStr" r="AJ9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">14:22</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK9">
@@ -1747,7 +1747,7 @@
       </c>
       <c s="20" t="inlineStr" r="AJ13">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK13">
@@ -2058,7 +2058,7 @@
       <c s="13" t="str" r="N17"/>
       <c s="12" t="inlineStr" r="O17">
         <is>
-          <t xml:space="preserve">21.5</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c s="13" t="str" r="P17"/>
@@ -2077,7 +2077,7 @@
       <c s="13" t="str" r="U17"/>
       <c s="12" t="inlineStr" r="V17">
         <is>
-          <t xml:space="preserve">4.5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c s="13" t="str" r="W17"/>
@@ -2095,7 +2095,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB17">
         <is>
-          <t xml:space="preserve">26.5</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c s="13" t="str" r="AC17"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE17">
         <is>
-          <t xml:space="preserve">17:53</t>
+          <t xml:space="preserve">18:41</t>
         </is>
       </c>
       <c s="13" t="str" r="AF17"/>
@@ -2118,13 +2118,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI17">
         <is>
-          <t xml:space="preserve">175:8</t>
+          <t xml:space="preserve">193:21</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ17"/>
       <c s="12" t="inlineStr" r="AK17">
         <is>
-          <t xml:space="preserve">14:7</t>
+          <t xml:space="preserve">14:20</t>
         </is>
       </c>
       <c s="13" t="str" r="AL17"/>
@@ -2449,12 +2449,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ19">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:59</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK19">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:49</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL19">
@@ -2611,7 +2611,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI20">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:03</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ20">
@@ -2621,7 +2621,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK20">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:53</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL20">
@@ -2778,7 +2778,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI21">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:09</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ21">
@@ -2788,7 +2788,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK21">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL21">
@@ -2945,7 +2945,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI22">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:09</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ22">
@@ -2955,7 +2955,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK22">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL22">
@@ -3117,17 +3117,17 @@
       </c>
       <c s="20" t="inlineStr" r="AJ23">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK23">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL23">
         <is>
-          <t xml:space="preserve">P-LT</t>
+          <t xml:space="preserve">P/2</t>
         </is>
       </c>
       <c s="21" t="str" r="AM23"/>
@@ -3428,7 +3428,7 @@
       <c s="13" t="str" r="N27"/>
       <c s="12" t="inlineStr" r="O27">
         <is>
-          <t xml:space="preserve">18.5</t>
+          <t xml:space="preserve">19.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P27"/>
@@ -3447,7 +3447,7 @@
       <c s="13" t="str" r="U27"/>
       <c s="12" t="inlineStr" r="V27">
         <is>
-          <t xml:space="preserve">7.5</t>
+          <t xml:space="preserve">6.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W27"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB27">
         <is>
-          <t xml:space="preserve">23.5</t>
+          <t xml:space="preserve">24.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC27"/>
@@ -3476,7 +3476,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE27">
         <is>
-          <t xml:space="preserve">29:53</t>
+          <t xml:space="preserve">30:17</t>
         </is>
       </c>
       <c s="13" t="str" r="AF27"/>
@@ -3488,7 +3488,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI27">
         <is>
-          <t xml:space="preserve">133:4</t>
+          <t xml:space="preserve">141:59</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ27"/>
@@ -3819,7 +3819,7 @@
       </c>
       <c s="18" t="inlineStr" r="AJ29">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:24</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK29">
@@ -3981,7 +3981,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI30">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:03</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ30">
@@ -4148,7 +4148,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI31">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:55</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ31">
@@ -4487,7 +4487,7 @@
       </c>
       <c s="20" t="inlineStr" r="AJ33">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK33">
@@ -4798,7 +4798,7 @@
       <c s="13" t="str" r="N37"/>
       <c s="12" t="inlineStr" r="O37">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P37"/>
@@ -4817,7 +4817,7 @@
       <c s="13" t="str" r="U37"/>
       <c s="12" t="inlineStr" r="V37">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W37"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB37">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">28.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC37"/>
@@ -4846,7 +4846,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE37">
         <is>
-          <t xml:space="preserve">1:17</t>
+          <t xml:space="preserve">1:44</t>
         </is>
       </c>
       <c s="13" t="str" r="AF37"/>
@@ -4858,13 +4858,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI37">
         <is>
-          <t xml:space="preserve">177:22</t>
+          <t xml:space="preserve">195:18</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ37"/>
       <c s="12" t="inlineStr" r="AK37">
         <is>
-          <t xml:space="preserve">6:25</t>
+          <t xml:space="preserve">6:36</t>
         </is>
       </c>
       <c s="13" t="str" r="AL37"/>
@@ -5189,12 +5189,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ39">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:57</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK39">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:12</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL39">
@@ -5351,7 +5351,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI40">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ40">
@@ -5361,7 +5361,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK40">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:57</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL40">
@@ -5518,7 +5518,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI41">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:11</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ41">
@@ -5528,7 +5528,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK41">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:45</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL41">
@@ -5685,7 +5685,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI42">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:11</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ42">
@@ -5857,12 +5857,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ43">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK43">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P/2</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL43">
@@ -6168,7 +6168,7 @@
       <c s="13" t="str" r="N47"/>
       <c s="12" t="inlineStr" r="O47">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c s="13" t="str" r="P47"/>
@@ -6187,7 +6187,7 @@
       <c s="13" t="str" r="U47"/>
       <c s="12" t="inlineStr" r="V47">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c s="13" t="str" r="W47"/>
@@ -6205,7 +6205,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB47">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c s="13" t="str" r="AC47"/>
@@ -6216,7 +6216,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE47">
         <is>
-          <t xml:space="preserve">1:4</t>
+          <t xml:space="preserve">1:28</t>
         </is>
       </c>
       <c s="13" t="str" r="AF47"/>
@@ -6228,7 +6228,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI47">
         <is>
-          <t xml:space="preserve">170:38</t>
+          <t xml:space="preserve">185:33</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ47"/>
@@ -6559,12 +6559,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ49">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:39</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK49">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:20</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL49">
@@ -6726,12 +6726,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ50">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">17:37</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK50">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:17</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL50">
@@ -6893,12 +6893,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ51">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">05:58</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK51">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:57</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL51">
@@ -7227,12 +7227,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ53">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK53">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL53">
@@ -7538,7 +7538,7 @@
       <c s="13" t="str" r="N57"/>
       <c s="12" t="inlineStr" r="O57">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c s="13" t="str" r="P57"/>
@@ -7557,7 +7557,7 @@
       <c s="13" t="str" r="U57"/>
       <c s="12" t="inlineStr" r="V57">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c s="13" t="str" r="W57"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB57">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c s="13" t="str" r="AC57"/>
@@ -7586,7 +7586,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE57">
         <is>
-          <t xml:space="preserve">00:21</t>
+          <t xml:space="preserve">11:50</t>
         </is>
       </c>
       <c s="13" t="str" r="AF57"/>
@@ -7596,9 +7596,17 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c s="12" t="str" r="AI57"/>
+      <c s="12" t="inlineStr" r="AI57">
+        <is>
+          <t xml:space="preserve">15:40</t>
+        </is>
+      </c>
       <c s="13" t="str" r="AJ57"/>
-      <c s="12" t="str" r="AK57"/>
+      <c s="12" t="inlineStr" r="AK57">
+        <is>
+          <t xml:space="preserve">00:17</t>
+        </is>
+      </c>
       <c s="13" t="str" r="AL57"/>
       <c s="13" t="str" r="AM57"/>
     </row>
@@ -7916,17 +7924,17 @@
       </c>
       <c s="18" t="inlineStr" r="AI59">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">14:39</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AJ59">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:20</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK59">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:36</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL59">
@@ -8083,7 +8091,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI60">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:02</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ60">
@@ -8093,7 +8101,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK60">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:53</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL60">
@@ -8250,7 +8258,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI61">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">06:23</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ61">
@@ -8260,7 +8268,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK61">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:17</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL61">
@@ -8427,7 +8435,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK62">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:17</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL62">
@@ -8584,17 +8592,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI63">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ63">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK63">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL63">
@@ -9402,7 +9410,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -9421,7 +9429,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -9439,7 +9447,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -9462,13 +9470,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI6">
         <is>
-          <t xml:space="preserve">175:8</t>
+          <t xml:space="preserve">184:43</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ6"/>
       <c s="12" t="inlineStr" r="AK6">
         <is>
-          <t xml:space="preserve">15:33</t>
+          <t xml:space="preserve">16:8</t>
         </is>
       </c>
       <c s="13" t="str" r="AL6"/>
@@ -9793,12 +9801,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:39</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:32</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL8">
@@ -9955,7 +9963,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:02</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ9">
@@ -10122,7 +10130,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:35</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ10">
@@ -10289,7 +10297,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI11">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:35</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ11">
@@ -10461,12 +10469,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL12">
@@ -10984,7 +10992,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -11003,7 +11011,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -11021,7 +11029,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -11032,7 +11040,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE6">
         <is>
-          <t xml:space="preserve">1:27</t>
+          <t xml:space="preserve">2:40</t>
         </is>
       </c>
       <c s="13" t="str" r="AF6"/>
@@ -11044,13 +11052,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI6">
         <is>
-          <t xml:space="preserve">214:18</t>
+          <t xml:space="preserve">232:5</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ6"/>
       <c s="12" t="inlineStr" r="AK6">
         <is>
-          <t xml:space="preserve">19:1</t>
+          <t xml:space="preserve">19:25</t>
         </is>
       </c>
       <c s="13" t="str" r="AL6"/>
@@ -11375,12 +11383,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:57</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:58</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL8">
@@ -11537,12 +11545,12 @@
       </c>
       <c s="20" t="inlineStr" r="AI9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:02</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:20</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK9">
@@ -11704,12 +11712,12 @@
       </c>
       <c s="20" t="inlineStr" r="AI10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:24</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:23</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK10">
@@ -11871,7 +11879,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI11">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:24</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ11">
@@ -12043,12 +12051,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL12">
@@ -12354,7 +12362,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -12373,7 +12381,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -12391,7 +12399,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -12414,13 +12422,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI16">
         <is>
-          <t xml:space="preserve">175:27</t>
+          <t xml:space="preserve">201:52</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ16"/>
       <c s="12" t="inlineStr" r="AK16">
         <is>
-          <t xml:space="preserve">14:25</t>
+          <t xml:space="preserve">14:43</t>
         </is>
       </c>
       <c s="13" t="str" r="AL16"/>
@@ -12745,12 +12753,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ18">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:52</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK18">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:56</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL18">
@@ -12907,17 +12915,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI19">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:34</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ19">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:20</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK19">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:14</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL19">
@@ -13074,17 +13082,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI20">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:39</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ20">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:28</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK20">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:18</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL20">
@@ -13251,7 +13259,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK21">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:18</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL21">
@@ -13413,12 +13421,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ22">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK22">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL22">
@@ -15476,7 +15484,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -15495,7 +15503,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -15513,7 +15521,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -15524,7 +15532,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE6">
         <is>
-          <t xml:space="preserve">7:43</t>
+          <t xml:space="preserve">8:55</t>
         </is>
       </c>
       <c s="13" t="str" r="AF6"/>
@@ -15536,7 +15544,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI6">
         <is>
-          <t xml:space="preserve">189:7</t>
+          <t xml:space="preserve">205:27</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ6"/>
@@ -15867,12 +15875,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:10</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:02</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL8">
@@ -16034,12 +16042,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">19:58</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:34</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL9">
@@ -16201,12 +16209,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">07:48</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:32</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL10">
@@ -16535,12 +16543,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL12">
@@ -16846,7 +16854,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -16865,7 +16873,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -16883,7 +16891,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -16894,7 +16902,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE16">
         <is>
-          <t xml:space="preserve">10:5</t>
+          <t xml:space="preserve">10:29</t>
         </is>
       </c>
       <c s="13" t="str" r="AF16"/>
@@ -16906,7 +16914,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI16">
         <is>
-          <t xml:space="preserve">85:38</t>
+          <t xml:space="preserve">103:1</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ16"/>
@@ -17233,12 +17241,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ18">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:39</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK18">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:20</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL18">
@@ -17395,7 +17403,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI19">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:09</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ19">
@@ -17405,7 +17413,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK19">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">19:59</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL19">
@@ -17562,7 +17570,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI20">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:44</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ20">
@@ -17572,7 +17580,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK20">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:39</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL20">
@@ -17901,12 +17909,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ22">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK22">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL22">
@@ -18212,7 +18220,7 @@
       <c s="13" t="str" r="N26"/>
       <c s="12" t="inlineStr" r="O26">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">21.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P26"/>
@@ -18231,7 +18239,7 @@
       <c s="13" t="str" r="U26"/>
       <c s="12" t="inlineStr" r="V26">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W26"/>
@@ -18249,7 +18257,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB26">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">26.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC26"/>
@@ -18260,7 +18268,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE26">
         <is>
-          <t xml:space="preserve">23:12</t>
+          <t xml:space="preserve">23:33</t>
         </is>
       </c>
       <c s="13" t="str" r="AF26"/>
@@ -18603,7 +18611,7 @@
       </c>
       <c s="18" t="inlineStr" r="AJ28">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:06</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK28">
@@ -19271,17 +19279,17 @@
       </c>
       <c s="20" t="inlineStr" r="AJ32">
         <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK32">
+        <is>
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c s="20" t="inlineStr" r="AK32">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
       <c s="20" t="inlineStr" r="AL32">
         <is>
-          <t xml:space="preserve">P-LT</t>
+          <t xml:space="preserve">P/2</t>
         </is>
       </c>
       <c s="21" t="str" r="AM32"/>
@@ -19582,7 +19590,7 @@
       <c s="13" t="str" r="N36"/>
       <c s="12" t="inlineStr" r="O36">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c s="13" t="str" r="P36"/>
@@ -19601,7 +19609,7 @@
       <c s="13" t="str" r="U36"/>
       <c s="12" t="inlineStr" r="V36">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c s="13" t="str" r="W36"/>
@@ -19619,7 +19627,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB36">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c s="13" t="str" r="AC36"/>
@@ -19630,7 +19638,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE36">
         <is>
-          <t xml:space="preserve">00:24</t>
+          <t xml:space="preserve">00:50</t>
         </is>
       </c>
       <c s="13" t="str" r="AF36"/>
@@ -19642,13 +19650,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI36">
         <is>
-          <t xml:space="preserve">181:3</t>
+          <t xml:space="preserve">205:2</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ36"/>
       <c s="12" t="inlineStr" r="AK36">
         <is>
-          <t xml:space="preserve">12:18</t>
+          <t xml:space="preserve">12:21</t>
         </is>
       </c>
       <c s="13" t="str" r="AL36"/>
@@ -19973,12 +19981,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ38">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:39</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK38">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:56</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL38">
@@ -20135,17 +20143,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI39">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:30</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ39">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">17:59</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK39">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:32</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL39">
@@ -20302,17 +20310,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI40">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:03</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ40">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">06:20</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK40">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:36</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL40">
@@ -20469,7 +20477,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI41">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:03</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ41">
@@ -20641,12 +20649,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ42">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK42">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL42">
@@ -21338,7 +21346,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -21357,7 +21365,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -21375,7 +21383,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -21386,7 +21394,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE6">
         <is>
-          <t xml:space="preserve">8:17</t>
+          <t xml:space="preserve">9:32</t>
         </is>
       </c>
       <c s="13" t="str" r="AF6"/>
@@ -21398,7 +21406,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI6">
         <is>
-          <t xml:space="preserve">178:19</t>
+          <t xml:space="preserve">203:22</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ6"/>
@@ -21729,12 +21737,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:09</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:36</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL8">
@@ -21891,17 +21899,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:07</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:21</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:15</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL9">
@@ -22058,17 +22066,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:12</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:12</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:39</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL10">
@@ -22397,12 +22405,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL12">
@@ -22708,7 +22716,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -22727,7 +22735,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -22745,7 +22753,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -22756,7 +22764,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE16">
         <is>
-          <t xml:space="preserve">2:2</t>
+          <t xml:space="preserve">2:32</t>
         </is>
       </c>
       <c s="13" t="str" r="AF16"/>
@@ -22768,13 +22776,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI16">
         <is>
-          <t xml:space="preserve">219:24</t>
+          <t xml:space="preserve">237:55</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ16"/>
       <c s="12" t="inlineStr" r="AK16">
         <is>
-          <t xml:space="preserve">32:42</t>
+          <t xml:space="preserve">33:38</t>
         </is>
       </c>
       <c s="13" t="str" r="AL16"/>
@@ -23099,12 +23107,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ18">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:45</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK18">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:20</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL18">
@@ -23266,12 +23274,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ19">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:20</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK19">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:16</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL19">
@@ -23433,12 +23441,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ20">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:35</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK20">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:56</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL20">
@@ -23605,7 +23613,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK21">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:56</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL21">
@@ -23767,12 +23775,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ22">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK22">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL22">
@@ -24078,7 +24086,7 @@
       <c s="13" t="str" r="N26"/>
       <c s="12" t="inlineStr" r="O26">
         <is>
-          <t xml:space="preserve">22.5</t>
+          <t xml:space="preserve">24.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P26"/>
@@ -24097,7 +24105,7 @@
       <c s="13" t="str" r="U26"/>
       <c s="12" t="inlineStr" r="V26">
         <is>
-          <t xml:space="preserve">3.5</t>
+          <t xml:space="preserve">1.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W26"/>
@@ -24115,7 +24123,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB26">
         <is>
-          <t xml:space="preserve">27.5</t>
+          <t xml:space="preserve">29.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC26"/>
@@ -24469,12 +24477,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ28">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:39</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK28">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:39</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL28">
@@ -25137,12 +25145,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ32">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK32">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL32">
@@ -25448,7 +25456,7 @@
       <c s="13" t="str" r="N36"/>
       <c s="12" t="inlineStr" r="O36">
         <is>
-          <t xml:space="preserve">19.5</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c s="13" t="str" r="P36"/>
@@ -25467,7 +25475,7 @@
       <c s="13" t="str" r="U36"/>
       <c s="12" t="inlineStr" r="V36">
         <is>
-          <t xml:space="preserve">6.5</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c s="13" t="str" r="W36"/>
@@ -25485,7 +25493,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB36">
         <is>
-          <t xml:space="preserve">24.5</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c s="13" t="str" r="AC36"/>
@@ -25496,7 +25504,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE36">
         <is>
-          <t xml:space="preserve">13:51</t>
+          <t xml:space="preserve">17:31</t>
         </is>
       </c>
       <c s="13" t="str" r="AF36"/>
@@ -25508,7 +25516,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI36">
         <is>
-          <t xml:space="preserve">101:0</t>
+          <t xml:space="preserve">108:12</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ36"/>
@@ -25839,12 +25847,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ38">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">13:08</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK38">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">13:32</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL38">
@@ -26006,7 +26014,7 @@
       </c>
       <c s="20" t="inlineStr" r="AJ39">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:20</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK39">
@@ -26173,7 +26181,7 @@
       </c>
       <c s="20" t="inlineStr" r="AJ40">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">07:12</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK40">
@@ -26507,12 +26515,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ42">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK42">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P/2</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL42">
@@ -26818,7 +26826,7 @@
       <c s="13" t="str" r="N46"/>
       <c s="12" t="inlineStr" r="O46">
         <is>
-          <t xml:space="preserve">21.5</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c s="13" t="str" r="P46"/>
@@ -26837,7 +26845,7 @@
       <c s="13" t="str" r="U46"/>
       <c s="12" t="inlineStr" r="V46">
         <is>
-          <t xml:space="preserve">4.5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c s="13" t="str" r="W46"/>
@@ -26855,7 +26863,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB46">
         <is>
-          <t xml:space="preserve">26.5</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c s="13" t="str" r="AC46"/>
@@ -26866,7 +26874,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE46">
         <is>
-          <t xml:space="preserve">5:39</t>
+          <t xml:space="preserve">6:54</t>
         </is>
       </c>
       <c s="13" t="str" r="AF46"/>
@@ -26878,7 +26886,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI46">
         <is>
-          <t xml:space="preserve">174:54</t>
+          <t xml:space="preserve">192:1</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ46"/>
@@ -27209,12 +27217,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ48">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:09</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK48">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:36</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL48">
@@ -27371,7 +27379,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI49">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:07</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ49">
@@ -27381,7 +27389,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK49">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">21:02</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL49">
@@ -27538,7 +27546,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI50">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:41</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ50">
@@ -27548,7 +27556,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK50">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:26</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL50">
@@ -27877,12 +27885,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ52">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK52">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P/2</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL52">
@@ -28188,7 +28196,7 @@
       <c s="13" t="str" r="N56"/>
       <c s="12" t="inlineStr" r="O56">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c s="13" t="str" r="P56"/>
@@ -28207,7 +28215,7 @@
       <c s="13" t="str" r="U56"/>
       <c s="12" t="inlineStr" r="V56">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c s="13" t="str" r="W56"/>
@@ -28225,7 +28233,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB56">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c s="13" t="str" r="AC56"/>
@@ -28236,7 +28244,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE56">
         <is>
-          <t xml:space="preserve">6:1</t>
+          <t xml:space="preserve">6:52</t>
         </is>
       </c>
       <c s="13" t="str" r="AF56"/>
@@ -28248,7 +28256,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI56">
         <is>
-          <t xml:space="preserve">107:20</t>
+          <t xml:space="preserve">131:16</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ56"/>
@@ -28579,12 +28587,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ58">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:01</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK58">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:20</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL58">
@@ -28741,17 +28749,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI59">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:15</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ59">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">19:58</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK59">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:31</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL59">
@@ -28908,17 +28916,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI60">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">07:48</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ60">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">07:57</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK60">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:11</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL60">
@@ -29247,17 +29255,17 @@
       </c>
       <c s="20" t="inlineStr" r="AJ62">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P/2</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK62">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL62">
         <is>
-          <t xml:space="preserve">P/2</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="21" t="str" r="AM62"/>
@@ -31422,7 +31430,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -31441,7 +31449,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -31459,7 +31467,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -31470,7 +31478,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE16">
         <is>
-          <t xml:space="preserve">32:44</t>
+          <t xml:space="preserve">35:36</t>
         </is>
       </c>
       <c s="13" t="str" r="AF16"/>
@@ -31805,7 +31813,7 @@
       </c>
       <c s="18" t="inlineStr" r="AJ18">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">13:52</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK18">
@@ -32473,17 +32481,17 @@
       </c>
       <c s="20" t="inlineStr" r="AJ22">
         <is>
+          <t xml:space="preserve">P/2</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK22">
+        <is>
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c s="20" t="inlineStr" r="AK22">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
       <c s="20" t="inlineStr" r="AL22">
         <is>
-          <t xml:space="preserve">P/2</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="21" t="str" r="AM22"/>
@@ -33054,7 +33062,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -33073,7 +33081,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -33091,7 +33099,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -33114,7 +33122,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI6">
         <is>
-          <t xml:space="preserve">151:31</t>
+          <t xml:space="preserve">164:47</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ6"/>
@@ -33445,12 +33453,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:40</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:44</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL8">
@@ -33612,12 +33620,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">16:10</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:30</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL9">
@@ -33779,12 +33787,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">04:30</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:46</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL10">
@@ -34113,12 +34121,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL12">
@@ -34424,7 +34432,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -34443,7 +34451,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -34461,7 +34469,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -34472,7 +34480,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE16">
         <is>
-          <t xml:space="preserve">00:32</t>
+          <t xml:space="preserve">00:50</t>
         </is>
       </c>
       <c s="13" t="str" r="AF16"/>
@@ -34807,12 +34815,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ18">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:03</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK18">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:50</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL18">
@@ -35475,12 +35483,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ22">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK22">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL22">
@@ -35786,7 +35794,7 @@
       <c s="13" t="str" r="N26"/>
       <c s="12" t="inlineStr" r="O26">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">21.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P26"/>
@@ -35805,7 +35813,7 @@
       <c s="13" t="str" r="U26"/>
       <c s="12" t="inlineStr" r="V26">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W26"/>
@@ -35823,7 +35831,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB26">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">26.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC26"/>
@@ -35834,7 +35842,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE26">
         <is>
-          <t xml:space="preserve">7:25</t>
+          <t xml:space="preserve">8:5</t>
         </is>
       </c>
       <c s="13" t="str" r="AF26"/>
@@ -35846,7 +35854,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI26">
         <is>
-          <t xml:space="preserve">179:8</t>
+          <t xml:space="preserve">187:18</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ26"/>
@@ -36177,7 +36185,7 @@
       </c>
       <c s="18" t="inlineStr" r="AJ28">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:10</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK28">
@@ -36344,7 +36352,7 @@
       </c>
       <c s="20" t="inlineStr" r="AJ29">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:20</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK29">
@@ -36511,7 +36519,7 @@
       </c>
       <c s="20" t="inlineStr" r="AJ30">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:10</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK30">
@@ -36845,17 +36853,17 @@
       </c>
       <c s="20" t="inlineStr" r="AJ32">
         <is>
+          <t xml:space="preserve">P-LT</t>
+        </is>
+      </c>
+      <c s="20" t="inlineStr" r="AK32">
+        <is>
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c s="20" t="inlineStr" r="AK32">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
       <c s="20" t="inlineStr" r="AL32">
         <is>
-          <t xml:space="preserve">P-LT</t>
+          <t xml:space="preserve">P/2</t>
         </is>
       </c>
       <c s="21" t="str" r="AM32"/>
@@ -37156,7 +37164,7 @@
       <c s="13" t="str" r="N36"/>
       <c s="12" t="inlineStr" r="O36">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c s="13" t="str" r="P36"/>
@@ -37175,7 +37183,7 @@
       <c s="13" t="str" r="U36"/>
       <c s="12" t="inlineStr" r="V36">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c s="13" t="str" r="W36"/>
@@ -37193,7 +37201,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB36">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c s="13" t="str" r="AC36"/>
@@ -37216,7 +37224,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI36">
         <is>
-          <t xml:space="preserve">188:14</t>
+          <t xml:space="preserve">214:25</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ36"/>
@@ -37547,12 +37555,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ38">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:39</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK38">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:20</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL38">
@@ -37709,17 +37717,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI39">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:11</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ39">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:19</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK39">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:05</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL39">
@@ -37876,17 +37884,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI40">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:46</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ40">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:40</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK40">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:45</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL40">
@@ -38215,12 +38223,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ42">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK42">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL42">
@@ -38526,7 +38534,7 @@
       <c s="13" t="str" r="N46"/>
       <c s="12" t="inlineStr" r="O46">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c s="13" t="str" r="P46"/>
@@ -38545,7 +38553,7 @@
       <c s="13" t="str" r="U46"/>
       <c s="12" t="inlineStr" r="V46">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c s="13" t="str" r="W46"/>
@@ -38563,7 +38571,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB46">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c s="13" t="str" r="AC46"/>
@@ -38586,7 +38594,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI46">
         <is>
-          <t xml:space="preserve">161:58</t>
+          <t xml:space="preserve">184:17</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ46"/>
@@ -38917,12 +38925,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ48">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:41</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK48">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:33</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL48">
@@ -39079,17 +39087,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI49">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:27</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ49">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">16:48</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK49">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:03</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL49">
@@ -39246,17 +39254,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI50">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:42</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ50">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">05:07</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK50">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:30</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL50">
@@ -39585,12 +39593,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ52">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK52">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL52">
@@ -39896,7 +39904,7 @@
       <c s="13" t="str" r="N56"/>
       <c s="12" t="inlineStr" r="O56">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c s="13" t="str" r="P56"/>
@@ -39915,7 +39923,7 @@
       <c s="13" t="str" r="U56"/>
       <c s="12" t="inlineStr" r="V56">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c s="13" t="str" r="W56"/>
@@ -39933,7 +39941,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB56">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c s="13" t="str" r="AC56"/>
@@ -39952,13 +39960,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI56">
         <is>
-          <t xml:space="preserve">202:54</t>
+          <t xml:space="preserve">226:22</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ56"/>
       <c s="12" t="inlineStr" r="AK56">
         <is>
-          <t xml:space="preserve">12:30</t>
+          <t xml:space="preserve">12:36</t>
         </is>
       </c>
       <c s="13" t="str" r="AL56"/>
@@ -40283,12 +40291,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ58">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:40</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK58">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:38</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL58">
@@ -40445,17 +40453,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI59">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:44</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ59">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">17:37</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK59">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:03</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL59">
@@ -40612,17 +40620,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI60">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:06</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ60">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">05:57</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK60">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:25</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL60">
@@ -40779,7 +40787,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI61">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:06</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ61">
@@ -40951,12 +40959,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ62">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK62">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL62">
@@ -41262,7 +41270,7 @@
       <c s="13" t="str" r="N66"/>
       <c s="12" t="inlineStr" r="O66">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c s="13" t="str" r="P66"/>
@@ -41281,7 +41289,7 @@
       <c s="13" t="str" r="U66"/>
       <c s="12" t="inlineStr" r="V66">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c s="13" t="str" r="W66"/>
@@ -41299,7 +41307,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB66">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c s="13" t="str" r="AC66"/>
@@ -41318,7 +41326,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI66">
         <is>
-          <t xml:space="preserve">153:53</t>
+          <t xml:space="preserve">170:26</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ66"/>
@@ -41654,7 +41662,7 @@
       </c>
       <c s="18" t="inlineStr" r="AK68">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:09</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL68">
@@ -41811,7 +41819,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI69">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:36</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ69">
@@ -41821,7 +41829,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK69">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:04</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL69">
@@ -41978,7 +41986,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI70">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:38</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ70">
@@ -41988,7 +41996,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK70">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">07:55</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL70">
@@ -42322,7 +42330,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK72">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL72">
@@ -42628,7 +42636,7 @@
       <c s="13" t="str" r="N76"/>
       <c s="12" t="inlineStr" r="O76">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c s="13" t="str" r="P76"/>
@@ -42647,7 +42655,7 @@
       <c s="13" t="str" r="U76"/>
       <c s="12" t="inlineStr" r="V76">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c s="13" t="str" r="W76"/>
@@ -42665,7 +42673,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB76">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c s="13" t="str" r="AC76"/>
@@ -42688,13 +42696,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI76">
         <is>
-          <t xml:space="preserve">138:17</t>
+          <t xml:space="preserve">165:0</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ76"/>
       <c s="12" t="inlineStr" r="AK76">
         <is>
-          <t xml:space="preserve">7:3</t>
+          <t xml:space="preserve">7:22</t>
         </is>
       </c>
       <c s="13" t="str" r="AL76"/>
@@ -43019,12 +43027,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ78">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:39</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK78">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:34</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL78">
@@ -43181,17 +43189,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI79">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:34</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ79">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:03</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK79">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:44</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL79">
@@ -43348,17 +43356,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI80">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:09</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ80">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:24</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK80">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:10</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL80">
@@ -43515,7 +43523,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI81">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:09</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ81">
@@ -43525,7 +43533,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK81">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:10</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL81">
@@ -43687,12 +43695,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ82">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK82">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL82">
@@ -47341,7 +47349,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">19.5</t>
+          <t xml:space="preserve">20.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -47360,7 +47368,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">6.5</t>
+          <t xml:space="preserve">5.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -47378,7 +47386,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">24.5</t>
+          <t xml:space="preserve">25.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -47389,7 +47397,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE6">
         <is>
-          <t xml:space="preserve">3:1</t>
+          <t xml:space="preserve">11:16</t>
         </is>
       </c>
       <c s="13" t="str" r="AF6"/>
@@ -47733,7 +47741,7 @@
       </c>
       <c s="18" t="inlineStr" r="AK8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:15</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL8">
@@ -48401,7 +48409,7 @@
       </c>
       <c s="20" t="inlineStr" r="AK12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL12">
@@ -50347,7 +50355,7 @@
       <c s="13" t="str" r="N6"/>
       <c s="12" t="inlineStr" r="O6">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c s="13" t="str" r="P6"/>
@@ -50366,7 +50374,7 @@
       <c s="13" t="str" r="U6"/>
       <c s="12" t="inlineStr" r="V6">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c s="13" t="str" r="W6"/>
@@ -50384,7 +50392,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB6">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c s="13" t="str" r="AC6"/>
@@ -50395,7 +50403,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE6">
         <is>
-          <t xml:space="preserve">00:38</t>
+          <t xml:space="preserve">1:2</t>
         </is>
       </c>
       <c s="13" t="str" r="AF6"/>
@@ -50407,7 +50415,7 @@
       </c>
       <c s="12" t="inlineStr" r="AI6">
         <is>
-          <t xml:space="preserve">190:24</t>
+          <t xml:space="preserve">214:32</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ6"/>
@@ -50738,12 +50746,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:39</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK8">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:20</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL8">
@@ -50900,17 +50908,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">19:37</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">19:17</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK9">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">19:37</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL9">
@@ -51067,17 +51075,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:13</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">07:38</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK10">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:17</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL10">
@@ -51406,12 +51414,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK12">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL12">
@@ -51717,7 +51725,7 @@
       <c s="13" t="str" r="N16"/>
       <c s="12" t="inlineStr" r="O16">
         <is>
-          <t xml:space="preserve">21.5</t>
+          <t xml:space="preserve">23.5</t>
         </is>
       </c>
       <c s="13" t="str" r="P16"/>
@@ -51736,7 +51744,7 @@
       <c s="13" t="str" r="U16"/>
       <c s="12" t="inlineStr" r="V16">
         <is>
-          <t xml:space="preserve">4.5</t>
+          <t xml:space="preserve">2.5</t>
         </is>
       </c>
       <c s="13" t="str" r="W16"/>
@@ -51754,7 +51762,7 @@
       </c>
       <c s="12" t="inlineStr" r="AB16">
         <is>
-          <t xml:space="preserve">26.5</t>
+          <t xml:space="preserve">28.5</t>
         </is>
       </c>
       <c s="13" t="str" r="AC16"/>
@@ -51765,7 +51773,7 @@
       </c>
       <c s="12" t="inlineStr" r="AE16">
         <is>
-          <t xml:space="preserve">10:7</t>
+          <t xml:space="preserve">10:51</t>
         </is>
       </c>
       <c s="13" t="str" r="AF16"/>
@@ -51777,13 +51785,13 @@
       </c>
       <c s="12" t="inlineStr" r="AI16">
         <is>
-          <t xml:space="preserve">166:12</t>
+          <t xml:space="preserve">190:44</t>
         </is>
       </c>
       <c s="13" t="str" r="AJ16"/>
       <c s="12" t="inlineStr" r="AK16">
         <is>
-          <t xml:space="preserve">5:30</t>
+          <t xml:space="preserve">5:36</t>
         </is>
       </c>
       <c s="13" t="str" r="AL16"/>
@@ -52108,12 +52116,12 @@
       </c>
       <c s="18" t="inlineStr" r="AJ18">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">11:39</t>
         </is>
       </c>
       <c s="18" t="inlineStr" r="AK18">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">12:14</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL18">
@@ -52270,17 +52278,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI19">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:45</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ19">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">18:42</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK19">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">20:37</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL19">
@@ -52437,17 +52445,17 @@
       </c>
       <c s="20" t="inlineStr" r="AI20">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">09:06</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ20">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">07:03</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK20">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">08:23</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL20">
@@ -52604,7 +52612,7 @@
       </c>
       <c s="20" t="inlineStr" r="AI21">
         <is>
-          <t xml:space="preserve">00:00</t>
+          <t xml:space="preserve">00:06</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AJ21">
@@ -52776,12 +52784,12 @@
       </c>
       <c s="20" t="inlineStr" r="AJ22">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AK22">
         <is>
-          <t xml:space="preserve">A</t>
+          <t xml:space="preserve">P-LT</t>
         </is>
       </c>
       <c s="20" t="inlineStr" r="AL22">
